--- a/research/traditional_assets/database/data/oman/oman_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_electrical_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="msm_ocai" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0675</v>
+        <v>-0.002100000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-0.0249</v>
       </c>
       <c r="G2">
-        <v>0.04188267394270122</v>
+        <v>0.03715482266719016</v>
       </c>
       <c r="H2">
-        <v>0.04188267394270122</v>
+        <v>0.03715482266719016</v>
       </c>
       <c r="I2">
-        <v>-0.01773533424283765</v>
+        <v>0.03364742834707499</v>
       </c>
       <c r="J2">
-        <v>-0.01773533424283765</v>
+        <v>0.03097227945022274</v>
       </c>
       <c r="K2">
-        <v>-2.16</v>
+        <v>19.56</v>
       </c>
       <c r="L2">
-        <v>-0.02946793997271487</v>
+        <v>0.02559874361994504</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>6.924</v>
       </c>
       <c r="N2">
-        <v>0.04362139917695473</v>
+        <v>0.01664023071377073</v>
       </c>
       <c r="O2">
-        <v>-0.4907407407407408</v>
+        <v>0.3539877300613496</v>
       </c>
       <c r="P2">
-        <v>1.06</v>
+        <v>6.924</v>
       </c>
       <c r="Q2">
-        <v>0.04362139917695473</v>
+        <v>0.01664023071377073</v>
       </c>
       <c r="R2">
-        <v>-0.4907407407407408</v>
+        <v>0.3539877300613496</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.43</v>
+        <v>84</v>
       </c>
       <c r="V2">
-        <v>0.0588477366255144</v>
+        <v>0.2018745493871665</v>
       </c>
       <c r="W2">
-        <v>-0.0416184971098266</v>
+        <v>-0.0009209770274728815</v>
       </c>
       <c r="X2">
-        <v>0.2002656007530126</v>
+        <v>0.2664178328846957</v>
       </c>
       <c r="Y2">
-        <v>-0.2418840978628392</v>
+        <v>-0.2673388099121686</v>
       </c>
       <c r="Z2">
-        <v>0.8763749402199904</v>
+        <v>2.311462020147019</v>
       </c>
       <c r="AA2">
-        <v>-0.0155428024868484</v>
+        <v>0.02740280813341266</v>
       </c>
       <c r="AB2">
-        <v>0.1078881131694221</v>
+        <v>0.1810185372276229</v>
       </c>
       <c r="AC2">
-        <v>-0.1234309156562705</v>
+        <v>-0.1536157290942102</v>
       </c>
       <c r="AD2">
-        <v>36.2</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>36.2</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="AG2">
-        <v>34.77</v>
+        <v>-35.59999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5983471074380166</v>
+        <v>0.1041980624327234</v>
       </c>
       <c r="AI2">
-        <v>0.414187643020595</v>
+        <v>0.1258123212893164</v>
       </c>
       <c r="AJ2">
-        <v>0.5886236668359573</v>
+        <v>-0.09356110381077529</v>
       </c>
       <c r="AK2">
-        <v>0.4044434104920321</v>
+        <v>-0.118390422347855</v>
       </c>
       <c r="AL2">
-        <v>1.6</v>
+        <v>4.68</v>
       </c>
       <c r="AM2">
-        <v>1.311</v>
+        <v>4.361</v>
       </c>
       <c r="AN2">
-        <v>32.90909090909091</v>
+        <v>1.323489198796828</v>
       </c>
       <c r="AO2">
-        <v>-0.8125</v>
+        <v>5.493589743589745</v>
       </c>
       <c r="AP2">
-        <v>31.60909090909091</v>
+        <v>-0.9734755263877494</v>
       </c>
       <c r="AQ2">
-        <v>-0.9916094584286803</v>
+        <v>5.89543682641596</v>
       </c>
     </row>
     <row r="3">
@@ -710,127 +715,8973 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Oman Cables Industry SAOG (MSM:OCAI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0172</v>
+      </c>
+      <c r="E3">
+        <v>-0.0249</v>
+      </c>
+      <c r="G3">
+        <v>0.03924812030075188</v>
+      </c>
+      <c r="H3">
+        <v>0.03924812030075188</v>
+      </c>
+      <c r="I3">
+        <v>0.0443609022556391</v>
+      </c>
+      <c r="J3">
+        <v>0.03730704854007811</v>
+      </c>
+      <c r="K3">
+        <v>23.8</v>
+      </c>
+      <c r="L3">
+        <v>0.03578947368421053</v>
+      </c>
+      <c r="M3">
+        <v>6.29</v>
+      </c>
+      <c r="N3">
+        <v>0.01584382871536524</v>
+      </c>
+      <c r="O3">
+        <v>0.2642857142857143</v>
+      </c>
+      <c r="P3">
+        <v>6.29</v>
+      </c>
+      <c r="Q3">
+        <v>0.01584382871536524</v>
+      </c>
+      <c r="R3">
+        <v>0.2642857142857143</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>91.5</v>
+      </c>
+      <c r="V3">
+        <v>0.2304785894206549</v>
+      </c>
+      <c r="W3">
+        <v>0.08558072635742538</v>
+      </c>
+      <c r="X3">
+        <v>0.1778000692089282</v>
+      </c>
+      <c r="Y3">
+        <v>-0.09221934285150281</v>
+      </c>
+      <c r="Z3">
+        <v>2.689041649818035</v>
+      </c>
+      <c r="AA3">
+        <v>0.1003202073560531</v>
+      </c>
+      <c r="AB3">
+        <v>0.1737815183702536</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07346131101420043</v>
+      </c>
+      <c r="AD3">
+        <v>17.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>17.8</v>
+      </c>
+      <c r="AG3">
+        <v>-73.7</v>
+      </c>
+      <c r="AH3">
+        <v>0.0429122468659595</v>
+      </c>
+      <c r="AI3">
+        <v>0.05760517799352751</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.227961645530467</v>
+      </c>
+      <c r="AK3">
+        <v>-0.3388505747126437</v>
+      </c>
+      <c r="AL3">
+        <v>2.78</v>
+      </c>
+      <c r="AM3">
+        <v>2.78</v>
+      </c>
+      <c r="AN3">
+        <v>0.4708994708994709</v>
+      </c>
+      <c r="AO3">
+        <v>10.61151079136691</v>
+      </c>
+      <c r="AP3">
+        <v>-1.94973544973545</v>
+      </c>
+      <c r="AQ3">
+        <v>10.61151079136691</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Voltamp Energy SAOG (MSM:VOES)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Electrical Equipment</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0214</v>
+      </c>
+      <c r="G4">
+        <v>0.0231079717457114</v>
+      </c>
+      <c r="H4">
+        <v>0.0231079717457114</v>
+      </c>
+      <c r="I4">
+        <v>-0.03824419778002018</v>
+      </c>
+      <c r="J4">
+        <v>-0.03824419778002018</v>
+      </c>
+      <c r="K4">
+        <v>-4.24</v>
+      </c>
+      <c r="L4">
+        <v>-0.04278506559031282</v>
+      </c>
+      <c r="M4">
+        <v>0.634</v>
+      </c>
+      <c r="N4">
+        <v>0.03319371727748691</v>
+      </c>
+      <c r="O4">
+        <v>-0.1495283018867924</v>
+      </c>
+      <c r="P4">
+        <v>0.634</v>
+      </c>
+      <c r="Q4">
+        <v>0.03319371727748691</v>
+      </c>
+      <c r="R4">
+        <v>-0.1495283018867924</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>-7.5</v>
+      </c>
+      <c r="V4">
+        <v>-0.3926701570680628</v>
+      </c>
+      <c r="W4">
+        <v>-0.08742268041237114</v>
+      </c>
+      <c r="X4">
+        <v>0.3550355965604632</v>
+      </c>
+      <c r="Y4">
+        <v>-0.4424582769728344</v>
+      </c>
+      <c r="Z4">
+        <v>1.190104479404347</v>
+      </c>
+      <c r="AA4">
+        <v>-0.04551459108922781</v>
+      </c>
+      <c r="AB4">
+        <v>0.1882555560849922</v>
+      </c>
+      <c r="AC4">
+        <v>-0.23377014717422</v>
+      </c>
+      <c r="AD4">
+        <v>30.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>30.6</v>
+      </c>
+      <c r="AG4">
+        <v>38.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.6156941649899397</v>
+      </c>
+      <c r="AI4">
+        <v>0.404227212681638</v>
+      </c>
+      <c r="AJ4">
+        <v>0.666083916083916</v>
+      </c>
+      <c r="AK4">
+        <v>0.4579326923076923</v>
+      </c>
+      <c r="AL4">
+        <v>1.9</v>
+      </c>
+      <c r="AM4">
+        <v>1.581</v>
+      </c>
+      <c r="AN4">
+        <v>-24.87804878048781</v>
+      </c>
+      <c r="AO4">
+        <v>-1.994736842105263</v>
+      </c>
+      <c r="AP4">
+        <v>-30.97560975609756</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.397216951296648</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Oman Cables Industry SAOG (MSM:OCAI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MSM:OCAI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0429122468659595</v>
+      </c>
+      <c r="F2">
+        <v>0.28</v>
+      </c>
+      <c r="G2">
+        <v>397</v>
+      </c>
+      <c r="H2">
+        <v>309.759877961698</v>
+      </c>
+      <c r="I2">
+        <v>323.3</v>
+      </c>
+      <c r="J2">
+        <v>334.403877961698</v>
+      </c>
+      <c r="K2">
+        <v>17.8</v>
+      </c>
+      <c r="L2">
+        <v>116.144</v>
+      </c>
+      <c r="M2">
+        <v>0.173781518370254</v>
+      </c>
+      <c r="N2">
+        <v>0.169299458185414</v>
+      </c>
+      <c r="O2">
+        <v>0.08415428899082571</v>
+      </c>
+      <c r="P2">
+        <v>0.04675</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.177800069208928</v>
+      </c>
+      <c r="T2">
+        <v>0.216957580813076</v>
+      </c>
+      <c r="U2">
+        <v>1.14670438486376</v>
+      </c>
+      <c r="V2">
+        <v>1.46974084457472</v>
+      </c>
+      <c r="W2">
+        <v>4.618091647985572</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>397</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.09900504587155964</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>37.8</v>
+      </c>
+      <c r="AH2">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="AI2">
+        <v>12.14</v>
+      </c>
+      <c r="AJ2">
+        <v>17.8</v>
+      </c>
+      <c r="AK2">
+        <v>17.8</v>
+      </c>
+      <c r="AL2">
+        <v>2.78</v>
+      </c>
+      <c r="AM2">
+        <v>17.8</v>
+      </c>
+      <c r="AN2">
+        <v>91.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1726971379805995</v>
+      </c>
+      <c r="C2">
+        <v>417.4182798621576</v>
+      </c>
+      <c r="D2">
+        <v>325.9182798621576</v>
+      </c>
+      <c r="E2">
+        <v>-17.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>91.5</v>
+      </c>
+      <c r="H2">
+        <v>397</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>37.8</v>
+      </c>
+      <c r="K2">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L2">
+        <v>29.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>29.5</v>
+      </c>
+      <c r="O2">
+        <v>4.425000000000001</v>
+      </c>
+      <c r="P2">
+        <v>25.075</v>
+      </c>
+      <c r="Q2">
+        <v>33.375</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1726971379805995</v>
+      </c>
+      <c r="T2">
+        <v>1.104606897801457</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1724967422736286</v>
+      </c>
+      <c r="C3">
+        <v>413.7587930674686</v>
+      </c>
       <c r="D3">
-        <v>-0.0675</v>
+        <v>326.4067930674686</v>
+      </c>
+      <c r="E3">
+        <v>-13.652</v>
+      </c>
+      <c r="F3">
+        <v>4.148000000000001</v>
       </c>
       <c r="G3">
-        <v>0.04188267394270122</v>
+        <v>91.5</v>
       </c>
       <c r="H3">
-        <v>0.04188267394270122</v>
+        <v>397</v>
       </c>
       <c r="I3">
-        <v>-0.01773533424283765</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.01773533424283765</v>
+        <v>37.8</v>
       </c>
       <c r="K3">
-        <v>-2.16</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="L3">
-        <v>-0.02946793997271487</v>
+        <v>29.5</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>0.1895636000000001</v>
       </c>
       <c r="N3">
-        <v>0.04362139917695473</v>
+        <v>29.3104364</v>
       </c>
       <c r="O3">
-        <v>-0.4907407407407408</v>
+        <v>4.396565460000001</v>
       </c>
       <c r="P3">
-        <v>1.06</v>
+        <v>24.91387094</v>
       </c>
       <c r="Q3">
-        <v>0.04362139917695473</v>
+        <v>33.21387093999999</v>
       </c>
       <c r="R3">
-        <v>-0.4907407407407408</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1738467598723522</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.114090896418944</v>
       </c>
       <c r="U3">
-        <v>1.43</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.0588477366255144</v>
+        <v>0.15</v>
       </c>
       <c r="W3">
-        <v>-0.0416184971098266</v>
-      </c>
-      <c r="X3">
-        <v>0.2002656007530126</v>
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.2418840978628392</v>
+        <v>155.6205938270849</v>
       </c>
       <c r="Z3">
-        <v>0.8763749402199904</v>
-      </c>
-      <c r="AA3">
-        <v>-0.0155428024868484</v>
-      </c>
-      <c r="AB3">
-        <v>0.1078881131694221</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1234309156562705</v>
-      </c>
-      <c r="AD3">
-        <v>36.2</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>36.2</v>
-      </c>
-      <c r="AG3">
-        <v>34.77</v>
-      </c>
-      <c r="AH3">
-        <v>0.5983471074380166</v>
-      </c>
-      <c r="AI3">
-        <v>0.414187643020595</v>
-      </c>
-      <c r="AJ3">
-        <v>0.5886236668359573</v>
-      </c>
-      <c r="AK3">
-        <v>0.4044434104920321</v>
-      </c>
-      <c r="AL3">
-        <v>1.6</v>
-      </c>
-      <c r="AM3">
-        <v>1.311</v>
-      </c>
-      <c r="AN3">
-        <v>32.90909090909091</v>
-      </c>
-      <c r="AO3">
-        <v>-0.8125</v>
-      </c>
-      <c r="AP3">
-        <v>31.60909090909091</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.9916094584286803</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1722963465666578</v>
+      </c>
+      <c r="C4">
+        <v>410.1007729188961</v>
+      </c>
+      <c r="D4">
+        <v>326.8967729188961</v>
+      </c>
+      <c r="E4">
+        <v>-9.504</v>
+      </c>
+      <c r="F4">
+        <v>8.296000000000001</v>
+      </c>
+      <c r="G4">
+        <v>91.5</v>
+      </c>
+      <c r="H4">
+        <v>397</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>37.8</v>
+      </c>
+      <c r="K4">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L4">
+        <v>29.5</v>
+      </c>
+      <c r="M4">
+        <v>0.3791272000000001</v>
+      </c>
+      <c r="N4">
+        <v>29.1208728</v>
+      </c>
+      <c r="O4">
+        <v>4.36813092</v>
+      </c>
+      <c r="P4">
+        <v>24.75274188</v>
+      </c>
+      <c r="Q4">
+        <v>33.05274188</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1750198434353651</v>
+      </c>
+      <c r="T4">
+        <v>1.123768446028625</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>77.81029691354246</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1720959508596868</v>
+      </c>
+      <c r="C5">
+        <v>406.4442260312607</v>
+      </c>
+      <c r="D5">
+        <v>327.3882260312607</v>
+      </c>
+      <c r="E5">
+        <v>-5.356000000000002</v>
+      </c>
+      <c r="F5">
+        <v>12.444</v>
+      </c>
+      <c r="G5">
+        <v>91.5</v>
+      </c>
+      <c r="H5">
+        <v>397</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>37.8</v>
+      </c>
+      <c r="K5">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L5">
+        <v>29.5</v>
+      </c>
+      <c r="M5">
+        <v>0.5686908000000001</v>
+      </c>
+      <c r="N5">
+        <v>28.9313092</v>
+      </c>
+      <c r="O5">
+        <v>4.339696380000001</v>
+      </c>
+      <c r="P5">
+        <v>24.59161282</v>
+      </c>
+      <c r="Q5">
+        <v>32.89161282</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1762171142883369</v>
+      </c>
+      <c r="T5">
+        <v>1.13364553274366</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>51.87353127569498</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.171895555152716</v>
+      </c>
+      <c r="C6">
+        <v>402.789159059221</v>
+      </c>
+      <c r="D6">
+        <v>327.881159059221</v>
+      </c>
+      <c r="E6">
+        <v>-1.207999999999998</v>
+      </c>
+      <c r="F6">
+        <v>16.592</v>
+      </c>
+      <c r="G6">
+        <v>91.5</v>
+      </c>
+      <c r="H6">
+        <v>397</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>37.8</v>
+      </c>
+      <c r="K6">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L6">
+        <v>29.5</v>
+      </c>
+      <c r="M6">
+        <v>0.7582544000000002</v>
+      </c>
+      <c r="N6">
+        <v>28.7417456</v>
+      </c>
+      <c r="O6">
+        <v>4.311261840000001</v>
+      </c>
+      <c r="P6">
+        <v>24.43048376</v>
+      </c>
+      <c r="Q6">
+        <v>32.73048376</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1774393282840791</v>
+      </c>
+      <c r="T6">
+        <v>1.143728392098592</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>38.90514845677123</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1716951594457451</v>
+      </c>
+      <c r="C7">
+        <v>399.1355786975746</v>
+      </c>
+      <c r="D7">
+        <v>328.3755786975746</v>
+      </c>
+      <c r="E7">
+        <v>2.940000000000001</v>
+      </c>
+      <c r="F7">
+        <v>20.74</v>
+      </c>
+      <c r="G7">
+        <v>91.5</v>
+      </c>
+      <c r="H7">
+        <v>397</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>37.8</v>
+      </c>
+      <c r="K7">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L7">
+        <v>29.5</v>
+      </c>
+      <c r="M7">
+        <v>0.9478180000000002</v>
+      </c>
+      <c r="N7">
+        <v>28.552182</v>
+      </c>
+      <c r="O7">
+        <v>4.2828273</v>
+      </c>
+      <c r="P7">
+        <v>24.2693547</v>
+      </c>
+      <c r="Q7">
+        <v>32.56935469999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1786872731007843</v>
+      </c>
+      <c r="T7">
+        <v>1.154023522176785</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>31.12411876541698</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1714947637387741</v>
+      </c>
+      <c r="C8">
+        <v>395.4834916815612</v>
+      </c>
+      <c r="D8">
+        <v>328.8714916815612</v>
+      </c>
+      <c r="E8">
+        <v>7.087999999999997</v>
+      </c>
+      <c r="F8">
+        <v>24.888</v>
+      </c>
+      <c r="G8">
+        <v>91.5</v>
+      </c>
+      <c r="H8">
+        <v>397</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>37.8</v>
+      </c>
+      <c r="K8">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L8">
+        <v>29.5</v>
+      </c>
+      <c r="M8">
+        <v>1.1373816</v>
+      </c>
+      <c r="N8">
+        <v>28.3626184</v>
+      </c>
+      <c r="O8">
+        <v>4.254392760000001</v>
+      </c>
+      <c r="P8">
+        <v>24.10822564</v>
+      </c>
+      <c r="Q8">
+        <v>32.40822564</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1799617699348661</v>
+      </c>
+      <c r="T8">
+        <v>1.164537697575791</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>25.93676563784749</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1712943680318032</v>
+      </c>
+      <c r="C9">
+        <v>391.8329047871679</v>
+      </c>
+      <c r="D9">
+        <v>329.3689047871679</v>
+      </c>
+      <c r="E9">
+        <v>11.236</v>
+      </c>
+      <c r="F9">
+        <v>29.036</v>
+      </c>
+      <c r="G9">
+        <v>91.5</v>
+      </c>
+      <c r="H9">
+        <v>397</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>37.8</v>
+      </c>
+      <c r="K9">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L9">
+        <v>29.5</v>
+      </c>
+      <c r="M9">
+        <v>1.3269452</v>
+      </c>
+      <c r="N9">
+        <v>28.1730548</v>
+      </c>
+      <c r="O9">
+        <v>4.225958220000001</v>
+      </c>
+      <c r="P9">
+        <v>23.94709658</v>
+      </c>
+      <c r="Q9">
+        <v>32.24709658</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1812636753030142</v>
+      </c>
+      <c r="T9">
+        <v>1.175277984273701</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>22.23151340386927</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1710939723248324</v>
+      </c>
+      <c r="C10">
+        <v>388.1838248314385</v>
+      </c>
+      <c r="D10">
+        <v>329.8678248314386</v>
+      </c>
+      <c r="E10">
+        <v>15.384</v>
+      </c>
+      <c r="F10">
+        <v>33.184</v>
+      </c>
+      <c r="G10">
+        <v>91.5</v>
+      </c>
+      <c r="H10">
+        <v>397</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>37.8</v>
+      </c>
+      <c r="K10">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L10">
+        <v>29.5</v>
+      </c>
+      <c r="M10">
+        <v>1.5165088</v>
+      </c>
+      <c r="N10">
+        <v>27.9834912</v>
+      </c>
+      <c r="O10">
+        <v>4.197523680000001</v>
+      </c>
+      <c r="P10">
+        <v>23.78596752</v>
+      </c>
+      <c r="Q10">
+        <v>32.08596752</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1825938829617743</v>
+      </c>
+      <c r="T10">
+        <v>1.186251755465043</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>19.45257422838561</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1708935766178614</v>
+      </c>
+      <c r="C11">
+        <v>384.5362586727849</v>
+      </c>
+      <c r="D11">
+        <v>330.3682586727849</v>
+      </c>
+      <c r="E11">
+        <v>19.532</v>
+      </c>
+      <c r="F11">
+        <v>37.332</v>
+      </c>
+      <c r="G11">
+        <v>91.5</v>
+      </c>
+      <c r="H11">
+        <v>397</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>37.8</v>
+      </c>
+      <c r="K11">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L11">
+        <v>29.5</v>
+      </c>
+      <c r="M11">
+        <v>1.7060724</v>
+      </c>
+      <c r="N11">
+        <v>27.7939276</v>
+      </c>
+      <c r="O11">
+        <v>4.169089140000001</v>
+      </c>
+      <c r="P11">
+        <v>23.62483846</v>
+      </c>
+      <c r="Q11">
+        <v>31.92483846</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1839533259536939</v>
+      </c>
+      <c r="T11">
+        <v>1.19746670844081</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>17.29117709189833</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1706931809108906</v>
+      </c>
+      <c r="C12">
+        <v>380.8902132113003</v>
+      </c>
+      <c r="D12">
+        <v>330.8702132113003</v>
+      </c>
+      <c r="E12">
+        <v>23.68</v>
+      </c>
+      <c r="F12">
+        <v>41.48</v>
+      </c>
+      <c r="G12">
+        <v>91.5</v>
+      </c>
+      <c r="H12">
+        <v>397</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>37.8</v>
+      </c>
+      <c r="K12">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L12">
+        <v>29.5</v>
+      </c>
+      <c r="M12">
+        <v>1.895636</v>
+      </c>
+      <c r="N12">
+        <v>27.604364</v>
+      </c>
+      <c r="O12">
+        <v>4.1406546</v>
+      </c>
+      <c r="P12">
+        <v>23.4637094</v>
+      </c>
+      <c r="Q12">
+        <v>31.7637094</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1853429787898784</v>
+      </c>
+      <c r="T12">
+        <v>1.208930882593817</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>15.56205938270849</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1704927852039197</v>
+      </c>
+      <c r="C13">
+        <v>377.2456953890782</v>
+      </c>
+      <c r="D13">
+        <v>331.3736953890782</v>
+      </c>
+      <c r="E13">
+        <v>27.828</v>
+      </c>
+      <c r="F13">
+        <v>45.628</v>
+      </c>
+      <c r="G13">
+        <v>91.5</v>
+      </c>
+      <c r="H13">
+        <v>397</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>37.8</v>
+      </c>
+      <c r="K13">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L13">
+        <v>29.5</v>
+      </c>
+      <c r="M13">
+        <v>2.0851996</v>
+      </c>
+      <c r="N13">
+        <v>27.4148004</v>
+      </c>
+      <c r="O13">
+        <v>4.11222006</v>
+      </c>
+      <c r="P13">
+        <v>23.30258034</v>
+      </c>
+      <c r="Q13">
+        <v>31.60258034</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.186763859779685</v>
+      </c>
+      <c r="T13">
+        <v>1.220652678637902</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.14732671155318</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1702923894969488</v>
+      </c>
+      <c r="C14">
+        <v>373.6027121905304</v>
+      </c>
+      <c r="D14">
+        <v>331.8787121905304</v>
+      </c>
+      <c r="E14">
+        <v>31.976</v>
+      </c>
+      <c r="F14">
+        <v>49.776</v>
+      </c>
+      <c r="G14">
+        <v>91.5</v>
+      </c>
+      <c r="H14">
+        <v>397</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>37.8</v>
+      </c>
+      <c r="K14">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L14">
+        <v>29.5</v>
+      </c>
+      <c r="M14">
+        <v>2.2747632</v>
+      </c>
+      <c r="N14">
+        <v>27.2252368</v>
+      </c>
+      <c r="O14">
+        <v>4.083785520000001</v>
+      </c>
+      <c r="P14">
+        <v>23.14145128</v>
+      </c>
+      <c r="Q14">
+        <v>31.44145128</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1882170335192599</v>
+      </c>
+      <c r="T14">
+        <v>1.232640879137535</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>12.96838281892374</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1702687937899779</v>
+      </c>
+      <c r="C15">
+        <v>369.5142769938345</v>
+      </c>
+      <c r="D15">
+        <v>331.9382769938345</v>
+      </c>
+      <c r="E15">
+        <v>36.12400000000001</v>
+      </c>
+      <c r="F15">
+        <v>53.92400000000001</v>
+      </c>
+      <c r="G15">
+        <v>91.5</v>
+      </c>
+      <c r="H15">
+        <v>397</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>37.8</v>
+      </c>
+      <c r="K15">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L15">
+        <v>29.5</v>
+      </c>
+      <c r="M15">
+        <v>2.550605200000001</v>
+      </c>
+      <c r="N15">
+        <v>26.9493948</v>
+      </c>
+      <c r="O15">
+        <v>4.042409220000001</v>
+      </c>
+      <c r="P15">
+        <v>22.90698558</v>
+      </c>
+      <c r="Q15">
+        <v>31.20698558</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1897036135516987</v>
+      </c>
+      <c r="T15">
+        <v>1.244904670453251</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.040205</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.56588248153811</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1700819980830069</v>
+      </c>
+      <c r="C16">
+        <v>365.8385781929872</v>
+      </c>
+      <c r="D16">
+        <v>332.4105781929872</v>
+      </c>
+      <c r="E16">
+        <v>40.27200000000001</v>
+      </c>
+      <c r="F16">
+        <v>58.07200000000001</v>
+      </c>
+      <c r="G16">
+        <v>91.5</v>
+      </c>
+      <c r="H16">
+        <v>397</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>37.8</v>
+      </c>
+      <c r="K16">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L16">
+        <v>29.5</v>
+      </c>
+      <c r="M16">
+        <v>2.746805600000001</v>
+      </c>
+      <c r="N16">
+        <v>26.7531944</v>
+      </c>
+      <c r="O16">
+        <v>4.01297916</v>
+      </c>
+      <c r="P16">
+        <v>22.74021524</v>
+      </c>
+      <c r="Q16">
+        <v>31.04021523999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1912247652127988</v>
+      </c>
+      <c r="T16">
+        <v>1.25745366621817</v>
+      </c>
+      <c r="U16">
+        <v>0.0473</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.040205</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>10.7397480185711</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1703797023760361</v>
+      </c>
+      <c r="C17">
+        <v>360.9384860815951</v>
+      </c>
+      <c r="D17">
+        <v>331.6584860815951</v>
+      </c>
+      <c r="E17">
+        <v>44.42</v>
+      </c>
+      <c r="F17">
+        <v>62.22</v>
+      </c>
+      <c r="G17">
+        <v>91.5</v>
+      </c>
+      <c r="H17">
+        <v>397</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>37.8</v>
+      </c>
+      <c r="K17">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L17">
+        <v>29.5</v>
+      </c>
+      <c r="M17">
+        <v>3.179442</v>
+      </c>
+      <c r="N17">
+        <v>26.320558</v>
+      </c>
+      <c r="O17">
+        <v>3.9480837</v>
+      </c>
+      <c r="P17">
+        <v>22.3724743</v>
+      </c>
+      <c r="Q17">
+        <v>30.67247429999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1927817086776895</v>
+      </c>
+      <c r="T17">
+        <v>1.270297932471675</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.043435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>9.278357648920785</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1702252066690652</v>
+      </c>
+      <c r="C18">
+        <v>357.1803641999465</v>
+      </c>
+      <c r="D18">
+        <v>332.0483641999465</v>
+      </c>
+      <c r="E18">
+        <v>48.56800000000001</v>
+      </c>
+      <c r="F18">
+        <v>66.36800000000001</v>
+      </c>
+      <c r="G18">
+        <v>91.5</v>
+      </c>
+      <c r="H18">
+        <v>397</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>37.8</v>
+      </c>
+      <c r="K18">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L18">
+        <v>29.5</v>
+      </c>
+      <c r="M18">
+        <v>3.391404800000001</v>
+      </c>
+      <c r="N18">
+        <v>26.1085952</v>
+      </c>
+      <c r="O18">
+        <v>3.91628928</v>
+      </c>
+      <c r="P18">
+        <v>22.19230592</v>
+      </c>
+      <c r="Q18">
+        <v>30.49230592</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1943757222250776</v>
+      </c>
+      <c r="T18">
+        <v>1.28344801458836</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.043435</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.698460295863235</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1700707109620943</v>
+      </c>
+      <c r="C19">
+        <v>353.423160032464</v>
+      </c>
+      <c r="D19">
+        <v>332.439160032464</v>
+      </c>
+      <c r="E19">
+        <v>52.71600000000001</v>
+      </c>
+      <c r="F19">
+        <v>70.51600000000001</v>
+      </c>
+      <c r="G19">
+        <v>91.5</v>
+      </c>
+      <c r="H19">
+        <v>397</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>37.8</v>
+      </c>
+      <c r="K19">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L19">
+        <v>29.5</v>
+      </c>
+      <c r="M19">
+        <v>3.6033676</v>
+      </c>
+      <c r="N19">
+        <v>25.8966324</v>
+      </c>
+      <c r="O19">
+        <v>3.884494860000001</v>
+      </c>
+      <c r="P19">
+        <v>22.01213754</v>
+      </c>
+      <c r="Q19">
+        <v>30.31213754</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.196008145737463</v>
+      </c>
+      <c r="T19">
+        <v>1.296914966153638</v>
+      </c>
+      <c r="U19">
+        <v>0.0511</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.043435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.186786160812456</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1702069152551234</v>
+      </c>
+      <c r="C20">
+        <v>348.93058424907</v>
+      </c>
+      <c r="D20">
+        <v>332.09458424907</v>
+      </c>
+      <c r="E20">
+        <v>56.864</v>
+      </c>
+      <c r="F20">
+        <v>74.664</v>
+      </c>
+      <c r="G20">
+        <v>91.5</v>
+      </c>
+      <c r="H20">
+        <v>397</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>37.8</v>
+      </c>
+      <c r="K20">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L20">
+        <v>29.5</v>
+      </c>
+      <c r="M20">
+        <v>3.957192</v>
+      </c>
+      <c r="N20">
+        <v>25.542808</v>
+      </c>
+      <c r="O20">
+        <v>3.831421200000001</v>
+      </c>
+      <c r="P20">
+        <v>21.7113868</v>
+      </c>
+      <c r="Q20">
+        <v>30.0113868</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1976803844574675</v>
+      </c>
+      <c r="T20">
+        <v>1.310710379952217</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>7.454781066978807</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1700685695481524</v>
+      </c>
+      <c r="C21">
+        <v>345.1325831878663</v>
+      </c>
+      <c r="D21">
+        <v>332.4445831878663</v>
+      </c>
+      <c r="E21">
+        <v>61.012</v>
+      </c>
+      <c r="F21">
+        <v>78.812</v>
+      </c>
+      <c r="G21">
+        <v>91.5</v>
+      </c>
+      <c r="H21">
+        <v>397</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>37.8</v>
+      </c>
+      <c r="K21">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L21">
+        <v>29.5</v>
+      </c>
+      <c r="M21">
+        <v>4.177036</v>
+      </c>
+      <c r="N21">
+        <v>25.322964</v>
+      </c>
+      <c r="O21">
+        <v>3.7984446</v>
+      </c>
+      <c r="P21">
+        <v>21.5245194</v>
+      </c>
+      <c r="Q21">
+        <v>29.8245194</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1993939130224104</v>
+      </c>
+      <c r="T21">
+        <v>1.324846421251994</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.062424168716764</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1699302238411816</v>
+      </c>
+      <c r="C22">
+        <v>341.3353206421505</v>
+      </c>
+      <c r="D22">
+        <v>332.7953206421505</v>
+      </c>
+      <c r="E22">
+        <v>65.16000000000001</v>
+      </c>
+      <c r="F22">
+        <v>82.96000000000001</v>
+      </c>
+      <c r="G22">
+        <v>91.5</v>
+      </c>
+      <c r="H22">
+        <v>397</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>37.8</v>
+      </c>
+      <c r="K22">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L22">
+        <v>29.5</v>
+      </c>
+      <c r="M22">
+        <v>4.396880000000001</v>
+      </c>
+      <c r="N22">
+        <v>25.10312</v>
+      </c>
+      <c r="O22">
+        <v>3.765468</v>
+      </c>
+      <c r="P22">
+        <v>21.337652</v>
+      </c>
+      <c r="Q22">
+        <v>29.637652</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.201150279801477</v>
+      </c>
+      <c r="T22">
+        <v>1.339335863584266</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.709302960280924</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1697918781342106</v>
+      </c>
+      <c r="C23">
+        <v>337.538798951849</v>
+      </c>
+      <c r="D23">
+        <v>333.146798951849</v>
+      </c>
+      <c r="E23">
+        <v>69.30800000000001</v>
+      </c>
+      <c r="F23">
+        <v>87.108</v>
+      </c>
+      <c r="G23">
+        <v>91.5</v>
+      </c>
+      <c r="H23">
+        <v>397</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>37.8</v>
+      </c>
+      <c r="K23">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L23">
+        <v>29.5</v>
+      </c>
+      <c r="M23">
+        <v>4.616724</v>
+      </c>
+      <c r="N23">
+        <v>24.883276</v>
+      </c>
+      <c r="O23">
+        <v>3.7324914</v>
+      </c>
+      <c r="P23">
+        <v>21.1507846</v>
+      </c>
+      <c r="Q23">
+        <v>29.4507846</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.202951111562292</v>
+      </c>
+      <c r="T23">
+        <v>1.354192127241406</v>
+      </c>
+      <c r="U23">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.389812343124691</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1700275324272398</v>
+      </c>
+      <c r="C24">
+        <v>332.7925443635793</v>
+      </c>
+      <c r="D24">
+        <v>332.5485443635793</v>
+      </c>
+      <c r="E24">
+        <v>73.456</v>
+      </c>
+      <c r="F24">
+        <v>91.256</v>
+      </c>
+      <c r="G24">
+        <v>91.5</v>
+      </c>
+      <c r="H24">
+        <v>397</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>37.8</v>
+      </c>
+      <c r="K24">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L24">
+        <v>29.5</v>
+      </c>
+      <c r="M24">
+        <v>5.01908</v>
+      </c>
+      <c r="N24">
+        <v>24.48092</v>
+      </c>
+      <c r="O24">
+        <v>3.672138000000001</v>
+      </c>
+      <c r="P24">
+        <v>20.808782</v>
+      </c>
+      <c r="Q24">
+        <v>29.108782</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2047981184964612</v>
+      </c>
+      <c r="T24">
+        <v>1.369429320735909</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.04675</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.877571188345275</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1699061867202689</v>
+      </c>
+      <c r="C25">
+        <v>328.9523356221569</v>
+      </c>
+      <c r="D25">
+        <v>332.8563356221569</v>
+      </c>
+      <c r="E25">
+        <v>77.60400000000001</v>
+      </c>
+      <c r="F25">
+        <v>95.40400000000001</v>
+      </c>
+      <c r="G25">
+        <v>91.5</v>
+      </c>
+      <c r="H25">
+        <v>397</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>37.8</v>
+      </c>
+      <c r="K25">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L25">
+        <v>29.5</v>
+      </c>
+      <c r="M25">
+        <v>5.24722</v>
+      </c>
+      <c r="N25">
+        <v>24.25278</v>
+      </c>
+      <c r="O25">
+        <v>3.637917000000001</v>
+      </c>
+      <c r="P25">
+        <v>20.614863</v>
+      </c>
+      <c r="Q25">
+        <v>28.914863</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2066930996367128</v>
+      </c>
+      <c r="T25">
+        <v>1.385062285490009</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.04675</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.622024614938958</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.169784841013298</v>
+      </c>
+      <c r="C26">
+        <v>325.1126971627241</v>
+      </c>
+      <c r="D26">
+        <v>333.1646971627241</v>
+      </c>
+      <c r="E26">
+        <v>81.752</v>
+      </c>
+      <c r="F26">
+        <v>99.55199999999999</v>
+      </c>
+      <c r="G26">
+        <v>91.5</v>
+      </c>
+      <c r="H26">
+        <v>397</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>37.8</v>
+      </c>
+      <c r="K26">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L26">
+        <v>29.5</v>
+      </c>
+      <c r="M26">
+        <v>5.475359999999999</v>
+      </c>
+      <c r="N26">
+        <v>24.02464</v>
+      </c>
+      <c r="O26">
+        <v>3.603696000000001</v>
+      </c>
+      <c r="P26">
+        <v>20.420944</v>
+      </c>
+      <c r="Q26">
+        <v>28.720944</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2086379487017078</v>
+      </c>
+      <c r="T26">
+        <v>1.401106644053427</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.04675</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.387773589316502</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.169663495306327</v>
+      </c>
+      <c r="C27">
+        <v>321.2736305716961</v>
+      </c>
+      <c r="D27">
+        <v>333.473630571696</v>
+      </c>
+      <c r="E27">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F27">
+        <v>103.7</v>
+      </c>
+      <c r="G27">
+        <v>91.5</v>
+      </c>
+      <c r="H27">
+        <v>397</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>37.8</v>
+      </c>
+      <c r="K27">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L27">
+        <v>29.5</v>
+      </c>
+      <c r="M27">
+        <v>5.7035</v>
+      </c>
+      <c r="N27">
+        <v>23.7965</v>
+      </c>
+      <c r="O27">
+        <v>3.569475000000001</v>
+      </c>
+      <c r="P27">
+        <v>20.227025</v>
+      </c>
+      <c r="Q27">
+        <v>28.527025</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2106346604084361</v>
+      </c>
+      <c r="T27">
+        <v>1.417578852178536</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.04675</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.172262645743841</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1695421495993562</v>
+      </c>
+      <c r="C28">
+        <v>317.4351374413771</v>
+      </c>
+      <c r="D28">
+        <v>333.7831374413771</v>
+      </c>
+      <c r="E28">
+        <v>90.04800000000002</v>
+      </c>
+      <c r="F28">
+        <v>107.848</v>
+      </c>
+      <c r="G28">
+        <v>91.5</v>
+      </c>
+      <c r="H28">
+        <v>397</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>37.8</v>
+      </c>
+      <c r="K28">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L28">
+        <v>29.5</v>
+      </c>
+      <c r="M28">
+        <v>5.931640000000001</v>
+      </c>
+      <c r="N28">
+        <v>23.56836</v>
+      </c>
+      <c r="O28">
+        <v>3.535254</v>
+      </c>
+      <c r="P28">
+        <v>20.033106</v>
+      </c>
+      <c r="Q28">
+        <v>28.33310599999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2126853372964272</v>
+      </c>
+      <c r="T28">
+        <v>1.434496255117838</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04675</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.973329467061385</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1694208038923853</v>
+      </c>
+      <c r="C29">
+        <v>313.5972193699889</v>
+      </c>
+      <c r="D29">
+        <v>334.093219369989</v>
+      </c>
+      <c r="E29">
+        <v>94.19600000000001</v>
+      </c>
+      <c r="F29">
+        <v>111.996</v>
+      </c>
+      <c r="G29">
+        <v>91.5</v>
+      </c>
+      <c r="H29">
+        <v>397</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>37.8</v>
+      </c>
+      <c r="K29">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L29">
+        <v>29.5</v>
+      </c>
+      <c r="M29">
+        <v>6.15978</v>
+      </c>
+      <c r="N29">
+        <v>23.34022</v>
+      </c>
+      <c r="O29">
+        <v>3.501033000000001</v>
+      </c>
+      <c r="P29">
+        <v>19.839187</v>
+      </c>
+      <c r="Q29">
+        <v>28.139187</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2147921971128565</v>
+      </c>
+      <c r="T29">
+        <v>1.451877148548627</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04675</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.789132079392445</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1692994581854144</v>
+      </c>
+      <c r="C30">
+        <v>309.7598779616977</v>
+      </c>
+      <c r="D30">
+        <v>334.4038779616977</v>
+      </c>
+      <c r="E30">
+        <v>98.34400000000002</v>
+      </c>
+      <c r="F30">
+        <v>116.144</v>
+      </c>
+      <c r="G30">
+        <v>91.5</v>
+      </c>
+      <c r="H30">
+        <v>397</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>37.8</v>
+      </c>
+      <c r="K30">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L30">
+        <v>29.5</v>
+      </c>
+      <c r="M30">
+        <v>6.387920000000001</v>
+      </c>
+      <c r="N30">
+        <v>23.11208</v>
+      </c>
+      <c r="O30">
+        <v>3.466812</v>
+      </c>
+      <c r="P30">
+        <v>19.645268</v>
+      </c>
+      <c r="Q30">
+        <v>27.945268</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2169575808130755</v>
+      </c>
+      <c r="T30">
+        <v>1.469740844574716</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04675</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.618091647985572</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1701148124784435</v>
+      </c>
+      <c r="C31">
+        <v>303.5355117669365</v>
+      </c>
+      <c r="D31">
+        <v>332.3275117669365</v>
+      </c>
+      <c r="E31">
+        <v>102.492</v>
+      </c>
+      <c r="F31">
+        <v>120.292</v>
+      </c>
+      <c r="G31">
+        <v>91.5</v>
+      </c>
+      <c r="H31">
+        <v>397</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>37.8</v>
+      </c>
+      <c r="K31">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L31">
+        <v>29.5</v>
+      </c>
+      <c r="M31">
+        <v>7.073169600000001</v>
+      </c>
+      <c r="N31">
+        <v>22.4268304</v>
+      </c>
+      <c r="O31">
+        <v>3.364024560000001</v>
+      </c>
+      <c r="P31">
+        <v>19.06280584</v>
+      </c>
+      <c r="Q31">
+        <v>27.36280584</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2191839612372443</v>
+      </c>
+      <c r="T31">
+        <v>1.488107743305766</v>
+      </c>
+      <c r="U31">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04998</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.170690322482865</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1700257667714725</v>
+      </c>
+      <c r="C32">
+        <v>299.6130188373788</v>
+      </c>
+      <c r="D32">
+        <v>332.5530188373788</v>
+      </c>
+      <c r="E32">
+        <v>106.64</v>
+      </c>
+      <c r="F32">
+        <v>124.44</v>
+      </c>
+      <c r="G32">
+        <v>91.5</v>
+      </c>
+      <c r="H32">
+        <v>397</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>37.8</v>
+      </c>
+      <c r="K32">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L32">
+        <v>29.5</v>
+      </c>
+      <c r="M32">
+        <v>7.317072</v>
+      </c>
+      <c r="N32">
+        <v>22.182928</v>
+      </c>
+      <c r="O32">
+        <v>3.327439200000001</v>
+      </c>
+      <c r="P32">
+        <v>18.8554888</v>
+      </c>
+      <c r="Q32">
+        <v>27.1554888</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2214739525306751</v>
+      </c>
+      <c r="T32">
+        <v>1.506999410571988</v>
+      </c>
+      <c r="U32">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04998</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.031667311733436</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1710434210645017</v>
+      </c>
+      <c r="C33">
+        <v>292.9059198322601</v>
+      </c>
+      <c r="D33">
+        <v>329.9939198322601</v>
+      </c>
+      <c r="E33">
+        <v>110.788</v>
+      </c>
+      <c r="F33">
+        <v>128.588</v>
+      </c>
+      <c r="G33">
+        <v>91.5</v>
+      </c>
+      <c r="H33">
+        <v>397</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>37.8</v>
+      </c>
+      <c r="K33">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L33">
+        <v>29.5</v>
+      </c>
+      <c r="M33">
+        <v>8.101044</v>
+      </c>
+      <c r="N33">
+        <v>21.398956</v>
+      </c>
+      <c r="O33">
+        <v>3.2098434</v>
+      </c>
+      <c r="P33">
+        <v>18.1891126</v>
+      </c>
+      <c r="Q33">
+        <v>26.4891126</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2238303203833358</v>
+      </c>
+      <c r="T33">
+        <v>1.526438662396651</v>
+      </c>
+      <c r="U33">
+        <v>0.063</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.05355</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.641505958985039</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1709900753575307</v>
+      </c>
+      <c r="C34">
+        <v>288.8910898822955</v>
+      </c>
+      <c r="D34">
+        <v>330.1270898822956</v>
+      </c>
+      <c r="E34">
+        <v>114.936</v>
+      </c>
+      <c r="F34">
+        <v>132.736</v>
+      </c>
+      <c r="G34">
+        <v>91.5</v>
+      </c>
+      <c r="H34">
+        <v>397</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>37.8</v>
+      </c>
+      <c r="K34">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L34">
+        <v>29.5</v>
+      </c>
+      <c r="M34">
+        <v>8.362368000000002</v>
+      </c>
+      <c r="N34">
+        <v>21.137632</v>
+      </c>
+      <c r="O34">
+        <v>3.1706448</v>
+      </c>
+      <c r="P34">
+        <v>17.9669872</v>
+      </c>
+      <c r="Q34">
+        <v>26.2669872</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2262559931728393</v>
+      </c>
+      <c r="T34">
+        <v>1.54644965692204</v>
+      </c>
+      <c r="U34">
+        <v>0.063</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.05355</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.527708897766756</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1729282796505598</v>
+      </c>
+      <c r="C35">
+        <v>279.9726287646099</v>
+      </c>
+      <c r="D35">
+        <v>325.3566287646099</v>
+      </c>
+      <c r="E35">
+        <v>119.084</v>
+      </c>
+      <c r="F35">
+        <v>136.884</v>
+      </c>
+      <c r="G35">
+        <v>91.5</v>
+      </c>
+      <c r="H35">
+        <v>397</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>37.8</v>
+      </c>
+      <c r="K35">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L35">
+        <v>29.5</v>
+      </c>
+      <c r="M35">
+        <v>9.595568400000001</v>
+      </c>
+      <c r="N35">
+        <v>19.9044316</v>
+      </c>
+      <c r="O35">
+        <v>2.98566474</v>
+      </c>
+      <c r="P35">
+        <v>16.91876686</v>
+      </c>
+      <c r="Q35">
+        <v>25.21876686</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2287540741053132</v>
+      </c>
+      <c r="T35">
+        <v>1.567057994567589</v>
+      </c>
+      <c r="U35">
+        <v>0.0701</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>3.074335856956634</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.179090983943589</v>
+      </c>
+      <c r="C36">
+        <v>261.5323582530609</v>
+      </c>
+      <c r="D36">
+        <v>311.064358253061</v>
+      </c>
+      <c r="E36">
+        <v>123.232</v>
+      </c>
+      <c r="F36">
+        <v>141.032</v>
+      </c>
+      <c r="G36">
+        <v>91.5</v>
+      </c>
+      <c r="H36">
+        <v>397</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>37.8</v>
+      </c>
+      <c r="K36">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L36">
+        <v>29.5</v>
+      </c>
+      <c r="M36">
+        <v>12.8903248</v>
+      </c>
+      <c r="N36">
+        <v>16.6096752</v>
+      </c>
+      <c r="O36">
+        <v>2.49145128</v>
+      </c>
+      <c r="P36">
+        <v>14.11822392</v>
+      </c>
+      <c r="Q36">
+        <v>22.41822392</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2313278544599833</v>
+      </c>
+      <c r="T36">
+        <v>1.588290827293307</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.288538144515955</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1792790382366181</v>
+      </c>
+      <c r="C37">
+        <v>256.9679474581686</v>
+      </c>
+      <c r="D37">
+        <v>310.6479474581686</v>
+      </c>
+      <c r="E37">
+        <v>127.38</v>
+      </c>
+      <c r="F37">
+        <v>145.18</v>
+      </c>
+      <c r="G37">
+        <v>91.5</v>
+      </c>
+      <c r="H37">
+        <v>397</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>37.8</v>
+      </c>
+      <c r="K37">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L37">
+        <v>29.5</v>
+      </c>
+      <c r="M37">
+        <v>13.269452</v>
+      </c>
+      <c r="N37">
+        <v>16.230548</v>
+      </c>
+      <c r="O37">
+        <v>2.4345822</v>
+      </c>
+      <c r="P37">
+        <v>13.7959658</v>
+      </c>
+      <c r="Q37">
+        <v>22.09596579999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2339808280563355</v>
+      </c>
+      <c r="T37">
+        <v>1.610176977949047</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.223151340386928</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1794670925296472</v>
+      </c>
+      <c r="C38">
+        <v>252.4046500414833</v>
+      </c>
+      <c r="D38">
+        <v>310.2326500414833</v>
+      </c>
+      <c r="E38">
+        <v>131.528</v>
+      </c>
+      <c r="F38">
+        <v>149.328</v>
+      </c>
+      <c r="G38">
+        <v>91.5</v>
+      </c>
+      <c r="H38">
+        <v>397</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>37.8</v>
+      </c>
+      <c r="K38">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L38">
+        <v>29.5</v>
+      </c>
+      <c r="M38">
+        <v>13.6485792</v>
+      </c>
+      <c r="N38">
+        <v>15.8514208</v>
+      </c>
+      <c r="O38">
+        <v>2.37771312</v>
+      </c>
+      <c r="P38">
+        <v>13.47370768</v>
+      </c>
+      <c r="Q38">
+        <v>21.77370767999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2367167070775737</v>
+      </c>
+      <c r="T38">
+        <v>1.632747070812778</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.161397136487291</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1796551468226763</v>
+      </c>
+      <c r="C39">
+        <v>247.842461543625</v>
+      </c>
+      <c r="D39">
+        <v>309.818461543625</v>
+      </c>
+      <c r="E39">
+        <v>135.676</v>
+      </c>
+      <c r="F39">
+        <v>153.476</v>
+      </c>
+      <c r="G39">
+        <v>91.5</v>
+      </c>
+      <c r="H39">
+        <v>397</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>37.8</v>
+      </c>
+      <c r="K39">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L39">
+        <v>29.5</v>
+      </c>
+      <c r="M39">
+        <v>14.0277064</v>
+      </c>
+      <c r="N39">
+        <v>15.4722936</v>
+      </c>
+      <c r="O39">
+        <v>2.32084404</v>
+      </c>
+      <c r="P39">
+        <v>13.15144956</v>
+      </c>
+      <c r="Q39">
+        <v>21.45144955999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2395394394010734</v>
+      </c>
+      <c r="T39">
+        <v>1.656033674561073</v>
+      </c>
+      <c r="U39">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.10298099766331</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1798432011157054</v>
+      </c>
+      <c r="C40">
+        <v>243.2813775289964</v>
+      </c>
+      <c r="D40">
+        <v>309.4053775289964</v>
+      </c>
+      <c r="E40">
+        <v>139.824</v>
+      </c>
+      <c r="F40">
+        <v>157.624</v>
+      </c>
+      <c r="G40">
+        <v>91.5</v>
+      </c>
+      <c r="H40">
+        <v>397</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>37.8</v>
+      </c>
+      <c r="K40">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L40">
+        <v>29.5</v>
+      </c>
+      <c r="M40">
+        <v>14.4068336</v>
+      </c>
+      <c r="N40">
+        <v>15.0931664</v>
+      </c>
+      <c r="O40">
+        <v>2.26397496</v>
+      </c>
+      <c r="P40">
+        <v>12.82919144</v>
+      </c>
+      <c r="Q40">
+        <v>21.12919144</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2424532276059764</v>
+      </c>
+      <c r="T40">
+        <v>1.680071459075442</v>
+      </c>
+      <c r="U40">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.047639392461644</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1870259054087345</v>
+      </c>
+      <c r="C41">
+        <v>224.1402673345562</v>
+      </c>
+      <c r="D41">
+        <v>294.4122673345562</v>
+      </c>
+      <c r="E41">
+        <v>143.972</v>
+      </c>
+      <c r="F41">
+        <v>161.772</v>
+      </c>
+      <c r="G41">
+        <v>91.5</v>
+      </c>
+      <c r="H41">
+        <v>397</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>37.8</v>
+      </c>
+      <c r="K41">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L41">
+        <v>29.5</v>
+      </c>
+      <c r="M41">
+        <v>18.19935</v>
+      </c>
+      <c r="N41">
+        <v>11.30065</v>
+      </c>
+      <c r="O41">
+        <v>1.6950975</v>
+      </c>
+      <c r="P41">
+        <v>9.605552499999998</v>
+      </c>
+      <c r="Q41">
+        <v>17.9055525</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2454625498503844</v>
+      </c>
+      <c r="T41">
+        <v>1.704897367672249</v>
+      </c>
+      <c r="U41">
+        <v>0.1125</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.095625</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.620937011486674</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1873933097017636</v>
+      </c>
+      <c r="C42">
+        <v>219.2643184709348</v>
+      </c>
+      <c r="D42">
+        <v>293.6843184709348</v>
+      </c>
+      <c r="E42">
+        <v>148.12</v>
+      </c>
+      <c r="F42">
+        <v>165.92</v>
+      </c>
+      <c r="G42">
+        <v>91.5</v>
+      </c>
+      <c r="H42">
+        <v>397</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>37.8</v>
+      </c>
+      <c r="K42">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L42">
+        <v>29.5</v>
+      </c>
+      <c r="M42">
+        <v>18.666</v>
+      </c>
+      <c r="N42">
+        <v>10.834</v>
+      </c>
+      <c r="O42">
+        <v>1.6251</v>
+      </c>
+      <c r="P42">
+        <v>9.208899999999996</v>
+      </c>
+      <c r="Q42">
+        <v>17.50889999999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2485721828362727</v>
+      </c>
+      <c r="T42">
+        <v>1.730550806555616</v>
+      </c>
+      <c r="U42">
+        <v>0.1125</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.095625</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.580413586199507</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1877607139947927</v>
+      </c>
+      <c r="C43">
+        <v>214.3919605076311</v>
+      </c>
+      <c r="D43">
+        <v>292.9599605076311</v>
+      </c>
+      <c r="E43">
+        <v>152.268</v>
+      </c>
+      <c r="F43">
+        <v>170.068</v>
+      </c>
+      <c r="G43">
+        <v>91.5</v>
+      </c>
+      <c r="H43">
+        <v>397</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>37.8</v>
+      </c>
+      <c r="K43">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L43">
+        <v>29.5</v>
+      </c>
+      <c r="M43">
+        <v>19.13265</v>
+      </c>
+      <c r="N43">
+        <v>10.36735</v>
+      </c>
+      <c r="O43">
+        <v>1.5551025</v>
+      </c>
+      <c r="P43">
+        <v>8.812247499999998</v>
+      </c>
+      <c r="Q43">
+        <v>17.1122475</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2517872271098181</v>
+      </c>
+      <c r="T43">
+        <v>1.757073853536724</v>
+      </c>
+      <c r="U43">
+        <v>0.1125</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.095625</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.541866913365373</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1881281182878217</v>
+      </c>
+      <c r="C44">
+        <v>209.5231669396798</v>
+      </c>
+      <c r="D44">
+        <v>292.2391669396798</v>
+      </c>
+      <c r="E44">
+        <v>156.416</v>
+      </c>
+      <c r="F44">
+        <v>174.216</v>
+      </c>
+      <c r="G44">
+        <v>91.5</v>
+      </c>
+      <c r="H44">
+        <v>397</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>37.8</v>
+      </c>
+      <c r="K44">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L44">
+        <v>29.5</v>
+      </c>
+      <c r="M44">
+        <v>19.5993</v>
+      </c>
+      <c r="N44">
+        <v>9.900699999999997</v>
+      </c>
+      <c r="O44">
+        <v>1.485105</v>
+      </c>
+      <c r="P44">
+        <v>8.415594999999998</v>
+      </c>
+      <c r="Q44">
+        <v>16.71559499999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.255113134979003</v>
+      </c>
+      <c r="T44">
+        <v>1.784511488344767</v>
+      </c>
+      <c r="U44">
+        <v>0.1125</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.095625</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.505155796380483</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2226178997929801</v>
+      </c>
+      <c r="C45">
+        <v>150.5422859941868</v>
+      </c>
+      <c r="D45">
+        <v>237.4062859941868</v>
+      </c>
+      <c r="E45">
+        <v>160.564</v>
+      </c>
+      <c r="F45">
+        <v>178.364</v>
+      </c>
+      <c r="G45">
+        <v>91.5</v>
+      </c>
+      <c r="H45">
+        <v>397</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>37.8</v>
+      </c>
+      <c r="K45">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L45">
+        <v>29.5</v>
+      </c>
+      <c r="M45">
+        <v>35.0663624</v>
+      </c>
+      <c r="N45">
+        <v>-5.566362400000003</v>
+      </c>
+      <c r="O45">
+        <v>-0.8349543600000006</v>
+      </c>
+      <c r="P45">
+        <v>-4.731408040000002</v>
+      </c>
+      <c r="Q45">
+        <v>3.568591959999995</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2609608622803977</v>
+      </c>
+      <c r="T45">
+        <v>1.832753295533494</v>
+      </c>
+      <c r="U45">
+        <v>0.1966</v>
+      </c>
+      <c r="V45">
+        <v>0.1261893078479107</v>
+      </c>
+      <c r="W45">
+        <v>0.1717911820771008</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.8412620523194044</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.22419589979298</v>
+      </c>
+      <c r="C46">
+        <v>144.3735988068372</v>
+      </c>
+      <c r="D46">
+        <v>235.3855988068372</v>
+      </c>
+      <c r="E46">
+        <v>164.712</v>
+      </c>
+      <c r="F46">
+        <v>182.512</v>
+      </c>
+      <c r="G46">
+        <v>91.5</v>
+      </c>
+      <c r="H46">
+        <v>397</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>37.8</v>
+      </c>
+      <c r="K46">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L46">
+        <v>29.5</v>
+      </c>
+      <c r="M46">
+        <v>35.8818592</v>
+      </c>
+      <c r="N46">
+        <v>-6.381859200000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.9572788800000003</v>
+      </c>
+      <c r="P46">
+        <v>-5.42458032</v>
+      </c>
+      <c r="Q46">
+        <v>2.875419679999997</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2649280205354048</v>
+      </c>
+      <c r="T46">
+        <v>1.865481032953735</v>
+      </c>
+      <c r="U46">
+        <v>0.1966</v>
+      </c>
+      <c r="V46">
+        <v>0.1233213690331855</v>
+      </c>
+      <c r="W46">
+        <v>0.1723550188480757</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8221424602212362</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.22577389979298</v>
+      </c>
+      <c r="C47">
+        <v>138.2390195285077</v>
+      </c>
+      <c r="D47">
+        <v>233.3990195285077</v>
+      </c>
+      <c r="E47">
+        <v>168.86</v>
+      </c>
+      <c r="F47">
+        <v>186.66</v>
+      </c>
+      <c r="G47">
+        <v>91.5</v>
+      </c>
+      <c r="H47">
+        <v>397</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>37.8</v>
+      </c>
+      <c r="K47">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L47">
+        <v>29.5</v>
+      </c>
+      <c r="M47">
+        <v>36.697356</v>
+      </c>
+      <c r="N47">
+        <v>-7.197355999999999</v>
+      </c>
+      <c r="O47">
+        <v>-1.0796034</v>
+      </c>
+      <c r="P47">
+        <v>-6.117752599999999</v>
+      </c>
+      <c r="Q47">
+        <v>2.182247399999998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2690394390905939</v>
+      </c>
+      <c r="T47">
+        <v>1.89939886991653</v>
+      </c>
+      <c r="U47">
+        <v>0.1966</v>
+      </c>
+      <c r="V47">
+        <v>0.1205808941657813</v>
+      </c>
+      <c r="W47">
+        <v>0.1728937962070074</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8038726277718755</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.235848397826045</v>
+      </c>
+      <c r="C48">
+        <v>122.1580224115504</v>
+      </c>
+      <c r="D48">
+        <v>221.4660224115504</v>
+      </c>
+      <c r="E48">
+        <v>173.008</v>
+      </c>
+      <c r="F48">
+        <v>190.808</v>
+      </c>
+      <c r="G48">
+        <v>91.5</v>
+      </c>
+      <c r="H48">
+        <v>397</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>37.8</v>
+      </c>
+      <c r="K48">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L48">
+        <v>29.5</v>
+      </c>
+      <c r="M48">
+        <v>40.79475040000001</v>
+      </c>
+      <c r="N48">
+        <v>-11.29475040000001</v>
+      </c>
+      <c r="O48">
+        <v>-1.694212560000001</v>
+      </c>
+      <c r="P48">
+        <v>-9.600537840000005</v>
+      </c>
+      <c r="Q48">
+        <v>-1.300537840000008</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2743855361720216</v>
+      </c>
+      <c r="T48">
+        <v>1.943502394469212</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1084698388055342</v>
+      </c>
+      <c r="W48">
+        <v>0.1906091484633768</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.7231322587035609</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.237598397826045</v>
+      </c>
+      <c r="C49">
+        <v>116.060481854592</v>
+      </c>
+      <c r="D49">
+        <v>219.5164818545921</v>
+      </c>
+      <c r="E49">
+        <v>177.156</v>
+      </c>
+      <c r="F49">
+        <v>194.956</v>
+      </c>
+      <c r="G49">
+        <v>91.5</v>
+      </c>
+      <c r="H49">
+        <v>397</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>37.8</v>
+      </c>
+      <c r="K49">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L49">
+        <v>29.5</v>
+      </c>
+      <c r="M49">
+        <v>41.6815928</v>
+      </c>
+      <c r="N49">
+        <v>-12.1815928</v>
+      </c>
+      <c r="O49">
+        <v>-1.827238920000001</v>
+      </c>
+      <c r="P49">
+        <v>-10.35435388</v>
+      </c>
+      <c r="Q49">
+        <v>-2.054353880000006</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2788305462884749</v>
+      </c>
+      <c r="T49">
+        <v>1.980172250968631</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1061619698947781</v>
+      </c>
+      <c r="W49">
+        <v>0.1911025708364964</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.7077464659651873</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.239348397826045</v>
+      </c>
+      <c r="C50">
+        <v>109.9969649648548</v>
+      </c>
+      <c r="D50">
+        <v>217.6009649648549</v>
+      </c>
+      <c r="E50">
+        <v>181.304</v>
+      </c>
+      <c r="F50">
+        <v>199.104</v>
+      </c>
+      <c r="G50">
+        <v>91.5</v>
+      </c>
+      <c r="H50">
+        <v>397</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>37.8</v>
+      </c>
+      <c r="K50">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L50">
+        <v>29.5</v>
+      </c>
+      <c r="M50">
+        <v>42.5684352</v>
+      </c>
+      <c r="N50">
+        <v>-13.0684352</v>
+      </c>
+      <c r="O50">
+        <v>-1.96026528</v>
+      </c>
+      <c r="P50">
+        <v>-11.10816992</v>
+      </c>
+      <c r="Q50">
+        <v>-2.808169919999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.283446518332484</v>
+      </c>
+      <c r="T50">
+        <v>2.018252486564182</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1039502621886369</v>
+      </c>
+      <c r="W50">
+        <v>0.1915754339440694</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6930017479242461</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.241098397826045</v>
+      </c>
+      <c r="C51">
+        <v>103.9665887682033</v>
+      </c>
+      <c r="D51">
+        <v>215.7185887682033</v>
+      </c>
+      <c r="E51">
+        <v>185.452</v>
+      </c>
+      <c r="F51">
+        <v>203.252</v>
+      </c>
+      <c r="G51">
+        <v>91.5</v>
+      </c>
+      <c r="H51">
+        <v>397</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>37.8</v>
+      </c>
+      <c r="K51">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L51">
+        <v>29.5</v>
+      </c>
+      <c r="M51">
+        <v>43.4552776</v>
+      </c>
+      <c r="N51">
+        <v>-13.9552776</v>
+      </c>
+      <c r="O51">
+        <v>-2.093291640000001</v>
+      </c>
+      <c r="P51">
+        <v>-11.86198596</v>
+      </c>
+      <c r="Q51">
+        <v>-3.561985960000005</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2882435088880229</v>
+      </c>
+      <c r="T51">
+        <v>2.057826064732107</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1018288282664198</v>
+      </c>
+      <c r="W51">
+        <v>0.1920289965166394</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6788588551094654</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.242848397826045</v>
+      </c>
+      <c r="C52">
+        <v>97.96850058144773</v>
+      </c>
+      <c r="D52">
+        <v>213.8685005814477</v>
+      </c>
+      <c r="E52">
+        <v>189.6</v>
+      </c>
+      <c r="F52">
+        <v>207.4</v>
+      </c>
+      <c r="G52">
+        <v>91.5</v>
+      </c>
+      <c r="H52">
+        <v>397</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>37.8</v>
+      </c>
+      <c r="K52">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L52">
+        <v>29.5</v>
+      </c>
+      <c r="M52">
+        <v>44.34212</v>
+      </c>
+      <c r="N52">
+        <v>-14.84212</v>
+      </c>
+      <c r="O52">
+        <v>-2.226318</v>
+      </c>
+      <c r="P52">
+        <v>-12.615802</v>
+      </c>
+      <c r="Q52">
+        <v>-4.315802000000003</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2932323790657834</v>
+      </c>
+      <c r="T52">
+        <v>2.098982586026749</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.09979225170109143</v>
+      </c>
+      <c r="W52">
+        <v>0.1924644165863066</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6652816780072761</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.244598397826045</v>
+      </c>
+      <c r="C53">
+        <v>92.00187672445395</v>
+      </c>
+      <c r="D53">
+        <v>212.049876724454</v>
+      </c>
+      <c r="E53">
+        <v>193.748</v>
+      </c>
+      <c r="F53">
+        <v>211.548</v>
+      </c>
+      <c r="G53">
+        <v>91.5</v>
+      </c>
+      <c r="H53">
+        <v>397</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>37.8</v>
+      </c>
+      <c r="K53">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L53">
+        <v>29.5</v>
+      </c>
+      <c r="M53">
+        <v>45.2289624</v>
+      </c>
+      <c r="N53">
+        <v>-15.7289624</v>
+      </c>
+      <c r="O53">
+        <v>-2.359344360000001</v>
+      </c>
+      <c r="P53">
+        <v>-13.36961804</v>
+      </c>
+      <c r="Q53">
+        <v>-5.069618040000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2984248765977381</v>
+      </c>
+      <c r="T53">
+        <v>2.141818965333417</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.09783554088342299</v>
+      </c>
+      <c r="W53">
+        <v>0.1928827613591242</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6522369392228198</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.246348397826045</v>
+      </c>
+      <c r="C54">
+        <v>86.06592129740784</v>
+      </c>
+      <c r="D54">
+        <v>210.2619212974079</v>
+      </c>
+      <c r="E54">
+        <v>197.896</v>
+      </c>
+      <c r="F54">
+        <v>215.696</v>
+      </c>
+      <c r="G54">
+        <v>91.5</v>
+      </c>
+      <c r="H54">
+        <v>397</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>37.8</v>
+      </c>
+      <c r="K54">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L54">
+        <v>29.5</v>
+      </c>
+      <c r="M54">
+        <v>46.11580480000001</v>
+      </c>
+      <c r="N54">
+        <v>-16.61580480000001</v>
+      </c>
+      <c r="O54">
+        <v>-2.492370720000001</v>
+      </c>
+      <c r="P54">
+        <v>-14.12343408000001</v>
+      </c>
+      <c r="Q54">
+        <v>-5.823434080000009</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3038337281935244</v>
+      </c>
+      <c r="T54">
+        <v>2.186440193777864</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.09595408817412636</v>
+      </c>
+      <c r="W54">
+        <v>0.1932850159483718</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.6396939211608423</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.248098397826045</v>
+      </c>
+      <c r="C55">
+        <v>80.15986501942203</v>
+      </c>
+      <c r="D55">
+        <v>208.5038650194221</v>
+      </c>
+      <c r="E55">
+        <v>202.044</v>
+      </c>
+      <c r="F55">
+        <v>219.844</v>
+      </c>
+      <c r="G55">
+        <v>91.5</v>
+      </c>
+      <c r="H55">
+        <v>397</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>37.8</v>
+      </c>
+      <c r="K55">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L55">
+        <v>29.5</v>
+      </c>
+      <c r="M55">
+        <v>47.00264720000001</v>
+      </c>
+      <c r="N55">
+        <v>-17.50264720000001</v>
+      </c>
+      <c r="O55">
+        <v>-2.625397080000001</v>
+      </c>
+      <c r="P55">
+        <v>-14.87725012</v>
+      </c>
+      <c r="Q55">
+        <v>-6.577250120000008</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3094727436870036</v>
+      </c>
+      <c r="T55">
+        <v>2.232960197900797</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.09414363368027492</v>
+      </c>
+      <c r="W55">
+        <v>0.1936720911191572</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.6276242245351661</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.249848397826045</v>
+      </c>
+      <c r="C56">
+        <v>74.28296412492324</v>
+      </c>
+      <c r="D56">
+        <v>206.7749641249233</v>
+      </c>
+      <c r="E56">
+        <v>206.192</v>
+      </c>
+      <c r="F56">
+        <v>223.992</v>
+      </c>
+      <c r="G56">
+        <v>91.5</v>
+      </c>
+      <c r="H56">
+        <v>397</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>37.8</v>
+      </c>
+      <c r="K56">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L56">
+        <v>29.5</v>
+      </c>
+      <c r="M56">
+        <v>47.8894896</v>
+      </c>
+      <c r="N56">
+        <v>-18.3894896</v>
+      </c>
+      <c r="O56">
+        <v>-2.758423440000001</v>
+      </c>
+      <c r="P56">
+        <v>-15.63106616</v>
+      </c>
+      <c r="Q56">
+        <v>-7.331066160000006</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3153569337671558</v>
+      </c>
+      <c r="T56">
+        <v>2.28150281089864</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.09240023305656614</v>
+      </c>
+      <c r="W56">
+        <v>0.1940448301725061</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.6160015537104409</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.251598397826045</v>
+      </c>
+      <c r="C57">
+        <v>68.43449931449535</v>
+      </c>
+      <c r="D57">
+        <v>205.0744993144953</v>
+      </c>
+      <c r="E57">
+        <v>210.34</v>
+      </c>
+      <c r="F57">
+        <v>228.14</v>
+      </c>
+      <c r="G57">
+        <v>91.5</v>
+      </c>
+      <c r="H57">
+        <v>397</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>37.8</v>
+      </c>
+      <c r="K57">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L57">
+        <v>29.5</v>
+      </c>
+      <c r="M57">
+        <v>48.776332</v>
+      </c>
+      <c r="N57">
+        <v>-19.276332</v>
+      </c>
+      <c r="O57">
+        <v>-2.891449800000001</v>
+      </c>
+      <c r="P57">
+        <v>-16.3848822</v>
+      </c>
+      <c r="Q57">
+        <v>-8.084882200000006</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.321502643406426</v>
+      </c>
+      <c r="T57">
+        <v>2.332202873363055</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.09072022881917402</v>
+      </c>
+      <c r="W57">
+        <v>0.1944040150784606</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.6048015254611601</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.253348397826045</v>
+      </c>
+      <c r="C58">
+        <v>62.61377475706772</v>
+      </c>
+      <c r="D58">
+        <v>203.4017747570678</v>
+      </c>
+      <c r="E58">
+        <v>214.488</v>
+      </c>
+      <c r="F58">
+        <v>232.288</v>
+      </c>
+      <c r="G58">
+        <v>91.5</v>
+      </c>
+      <c r="H58">
+        <v>397</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>37.8</v>
+      </c>
+      <c r="K58">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L58">
+        <v>29.5</v>
+      </c>
+      <c r="M58">
+        <v>49.6631744</v>
+      </c>
+      <c r="N58">
+        <v>-20.1631744</v>
+      </c>
+      <c r="O58">
+        <v>-3.024476160000001</v>
+      </c>
+      <c r="P58">
+        <v>-17.13869824</v>
+      </c>
+      <c r="Q58">
+        <v>-8.838698240000006</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3279277034838447</v>
+      </c>
+      <c r="T58">
+        <v>2.385207484121306</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.08910022473311736</v>
+      </c>
+      <c r="W58">
+        <v>0.1947503719520595</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5940014982207822</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.255098397826045</v>
+      </c>
+      <c r="C59">
+        <v>56.82011714054147</v>
+      </c>
+      <c r="D59">
+        <v>201.7561171405415</v>
+      </c>
+      <c r="E59">
+        <v>218.636</v>
+      </c>
+      <c r="F59">
+        <v>236.436</v>
+      </c>
+      <c r="G59">
+        <v>91.5</v>
+      </c>
+      <c r="H59">
+        <v>397</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>37.8</v>
+      </c>
+      <c r="K59">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L59">
+        <v>29.5</v>
+      </c>
+      <c r="M59">
+        <v>50.55001680000001</v>
+      </c>
+      <c r="N59">
+        <v>-21.05001680000001</v>
+      </c>
+      <c r="O59">
+        <v>-3.157502520000002</v>
+      </c>
+      <c r="P59">
+        <v>-17.89251428000001</v>
+      </c>
+      <c r="Q59">
+        <v>-9.59251428000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3346516035648644</v>
+      </c>
+      <c r="T59">
+        <v>2.440677425612499</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.08753706289569423</v>
+      </c>
+      <c r="W59">
+        <v>0.1950845759529006</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5835804193046281</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.256848397826045</v>
+      </c>
+      <c r="C60">
+        <v>51.05287476813197</v>
+      </c>
+      <c r="D60">
+        <v>200.136874768132</v>
+      </c>
+      <c r="E60">
+        <v>222.784</v>
+      </c>
+      <c r="F60">
+        <v>240.584</v>
+      </c>
+      <c r="G60">
+        <v>91.5</v>
+      </c>
+      <c r="H60">
+        <v>397</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>37.8</v>
+      </c>
+      <c r="K60">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L60">
+        <v>29.5</v>
+      </c>
+      <c r="M60">
+        <v>51.4368592</v>
+      </c>
+      <c r="N60">
+        <v>-21.9368592</v>
+      </c>
+      <c r="O60">
+        <v>-3.290528880000001</v>
+      </c>
+      <c r="P60">
+        <v>-18.64633032</v>
+      </c>
+      <c r="Q60">
+        <v>-10.34633032</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3416956893640277</v>
+      </c>
+      <c r="T60">
+        <v>2.498788792888987</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.08602780319059607</v>
+      </c>
+      <c r="W60">
+        <v>0.1954072556778506</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5735186879373071</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.258598397826045</v>
+      </c>
+      <c r="C61">
+        <v>45.31141669788062</v>
+      </c>
+      <c r="D61">
+        <v>198.5434166978806</v>
+      </c>
+      <c r="E61">
+        <v>226.932</v>
+      </c>
+      <c r="F61">
+        <v>244.732</v>
+      </c>
+      <c r="G61">
+        <v>91.5</v>
+      </c>
+      <c r="H61">
+        <v>397</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>37.8</v>
+      </c>
+      <c r="K61">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L61">
+        <v>29.5</v>
+      </c>
+      <c r="M61">
+        <v>52.3237016</v>
+      </c>
+      <c r="N61">
+        <v>-22.8237016</v>
+      </c>
+      <c r="O61">
+        <v>-3.423555240000001</v>
+      </c>
+      <c r="P61">
+        <v>-19.40014636</v>
+      </c>
+      <c r="Q61">
+        <v>-11.10014636</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3490833891046138</v>
+      </c>
+      <c r="T61">
+        <v>2.55973486100823</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.08456970483143342</v>
+      </c>
+      <c r="W61">
+        <v>0.1957189971070395</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.563798032209556</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.260348397826045</v>
+      </c>
+      <c r="C62">
+        <v>39.59513192294804</v>
+      </c>
+      <c r="D62">
+        <v>196.975131922948</v>
+      </c>
+      <c r="E62">
+        <v>231.08</v>
+      </c>
+      <c r="F62">
+        <v>248.88</v>
+      </c>
+      <c r="G62">
+        <v>91.5</v>
+      </c>
+      <c r="H62">
+        <v>397</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>37.8</v>
+      </c>
+      <c r="K62">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L62">
+        <v>29.5</v>
+      </c>
+      <c r="M62">
+        <v>53.210544</v>
+      </c>
+      <c r="N62">
+        <v>-23.710544</v>
+      </c>
+      <c r="O62">
+        <v>-3.5565816</v>
+      </c>
+      <c r="P62">
+        <v>-20.1539624</v>
+      </c>
+      <c r="Q62">
+        <v>-11.8539624</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3568404738322291</v>
+      </c>
+      <c r="T62">
+        <v>2.623728232533436</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.08316020975090954</v>
+      </c>
+      <c r="W62">
+        <v>0.1960203471552555</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5544013983393968</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.262098397826045</v>
+      </c>
+      <c r="C63">
+        <v>33.90342859045168</v>
+      </c>
+      <c r="D63">
+        <v>195.4314285904517</v>
+      </c>
+      <c r="E63">
+        <v>235.228</v>
+      </c>
+      <c r="F63">
+        <v>253.028</v>
+      </c>
+      <c r="G63">
+        <v>91.5</v>
+      </c>
+      <c r="H63">
+        <v>397</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>37.8</v>
+      </c>
+      <c r="K63">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L63">
+        <v>29.5</v>
+      </c>
+      <c r="M63">
+        <v>54.0973864</v>
+      </c>
+      <c r="N63">
+        <v>-24.5973864</v>
+      </c>
+      <c r="O63">
+        <v>-3.68960796</v>
+      </c>
+      <c r="P63">
+        <v>-20.90777844</v>
+      </c>
+      <c r="Q63">
+        <v>-12.60777844</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3649953577766453</v>
+      </c>
+      <c r="T63">
+        <v>2.691003315418909</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.08179692762384544</v>
+      </c>
+      <c r="W63">
+        <v>0.1963118168740218</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5453128508256362</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.263848397826045</v>
+      </c>
+      <c r="C64">
+        <v>28.23573325675</v>
+      </c>
+      <c r="D64">
+        <v>193.91173325675</v>
+      </c>
+      <c r="E64">
+        <v>239.376</v>
+      </c>
+      <c r="F64">
+        <v>257.176</v>
+      </c>
+      <c r="G64">
+        <v>91.5</v>
+      </c>
+      <c r="H64">
+        <v>397</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>37.8</v>
+      </c>
+      <c r="K64">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L64">
+        <v>29.5</v>
+      </c>
+      <c r="M64">
+        <v>54.9842288</v>
+      </c>
+      <c r="N64">
+        <v>-25.4842288</v>
+      </c>
+      <c r="O64">
+        <v>-3.82263432</v>
+      </c>
+      <c r="P64">
+        <v>-21.66159448</v>
+      </c>
+      <c r="Q64">
+        <v>-13.36159448</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3735794461391886</v>
+      </c>
+      <c r="T64">
+        <v>2.761819192140459</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.08047762233958987</v>
+      </c>
+      <c r="W64">
+        <v>0.1965938843437957</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5365174822639325</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.265598397826045</v>
+      </c>
+      <c r="C65">
+        <v>22.59149017720409</v>
+      </c>
+      <c r="D65">
+        <v>192.4154901772041</v>
+      </c>
+      <c r="E65">
+        <v>243.524</v>
+      </c>
+      <c r="F65">
+        <v>261.324</v>
+      </c>
+      <c r="G65">
+        <v>91.5</v>
+      </c>
+      <c r="H65">
+        <v>397</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>37.8</v>
+      </c>
+      <c r="K65">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L65">
+        <v>29.5</v>
+      </c>
+      <c r="M65">
+        <v>55.8710712</v>
+      </c>
+      <c r="N65">
+        <v>-26.3710712</v>
+      </c>
+      <c r="O65">
+        <v>-3.955660680000001</v>
+      </c>
+      <c r="P65">
+        <v>-22.41541052</v>
+      </c>
+      <c r="Q65">
+        <v>-14.11541052</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3826275392780856</v>
+      </c>
+      <c r="T65">
+        <v>2.836462954090202</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.07920019976277097</v>
+      </c>
+      <c r="W65">
+        <v>0.1968669972907196</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5280013317518064</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.267348397826045</v>
+      </c>
+      <c r="C66">
+        <v>16.97016062856989</v>
+      </c>
+      <c r="D66">
+        <v>190.9421606285699</v>
+      </c>
+      <c r="E66">
+        <v>247.672</v>
+      </c>
+      <c r="F66">
+        <v>265.472</v>
+      </c>
+      <c r="G66">
+        <v>91.5</v>
+      </c>
+      <c r="H66">
+        <v>397</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>37.8</v>
+      </c>
+      <c r="K66">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L66">
+        <v>29.5</v>
+      </c>
+      <c r="M66">
+        <v>56.7579136</v>
+      </c>
+      <c r="N66">
+        <v>-27.2579136</v>
+      </c>
+      <c r="O66">
+        <v>-4.088687040000001</v>
+      </c>
+      <c r="P66">
+        <v>-23.16922656</v>
+      </c>
+      <c r="Q66">
+        <v>-14.86922656</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3921783042580324</v>
+      </c>
+      <c r="T66">
+        <v>2.915253591703818</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.07796269664147769</v>
+      </c>
+      <c r="W66">
+        <v>0.1971315754580521</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5197513109431845</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.269098397826045</v>
+      </c>
+      <c r="C67">
+        <v>11.37122226228394</v>
+      </c>
+      <c r="D67">
+        <v>189.4912222622839</v>
+      </c>
+      <c r="E67">
+        <v>251.82</v>
+      </c>
+      <c r="F67">
+        <v>269.62</v>
+      </c>
+      <c r="G67">
+        <v>91.5</v>
+      </c>
+      <c r="H67">
+        <v>397</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>37.8</v>
+      </c>
+      <c r="K67">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L67">
+        <v>29.5</v>
+      </c>
+      <c r="M67">
+        <v>57.644756</v>
+      </c>
+      <c r="N67">
+        <v>-28.144756</v>
+      </c>
+      <c r="O67">
+        <v>-4.221713400000001</v>
+      </c>
+      <c r="P67">
+        <v>-23.9230426</v>
+      </c>
+      <c r="Q67">
+        <v>-15.62304260000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4022748272368334</v>
+      </c>
+      <c r="T67">
+        <v>2.998546551466785</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.0767632705393011</v>
+      </c>
+      <c r="W67">
+        <v>0.1973880127586974</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5117551369286739</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.270848397826045</v>
+      </c>
+      <c r="C68">
+        <v>5.794168487012485</v>
+      </c>
+      <c r="D68">
+        <v>188.0621684870125</v>
+      </c>
+      <c r="E68">
+        <v>255.968</v>
+      </c>
+      <c r="F68">
+        <v>273.768</v>
+      </c>
+      <c r="G68">
+        <v>91.5</v>
+      </c>
+      <c r="H68">
+        <v>397</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>37.8</v>
+      </c>
+      <c r="K68">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L68">
+        <v>29.5</v>
+      </c>
+      <c r="M68">
+        <v>58.5315984</v>
+      </c>
+      <c r="N68">
+        <v>-29.0315984</v>
+      </c>
+      <c r="O68">
+        <v>-4.354739760000001</v>
+      </c>
+      <c r="P68">
+        <v>-24.67685864</v>
+      </c>
+      <c r="Q68">
+        <v>-16.37685864</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4129652633320344</v>
+      </c>
+      <c r="T68">
+        <v>3.086739097098161</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.07560019068264504</v>
+      </c>
+      <c r="W68">
+        <v>0.1976366792320505</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5040012712176334</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2900478271023963</v>
+      </c>
+      <c r="C69">
+        <v>-12.72484655843147</v>
+      </c>
+      <c r="D69">
+        <v>173.6911534415685</v>
+      </c>
+      <c r="E69">
+        <v>260.116</v>
+      </c>
+      <c r="F69">
+        <v>277.916</v>
+      </c>
+      <c r="G69">
+        <v>91.5</v>
+      </c>
+      <c r="H69">
+        <v>397</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>37.8</v>
+      </c>
+      <c r="K69">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L69">
+        <v>29.5</v>
+      </c>
+      <c r="M69">
+        <v>66.3663408</v>
+      </c>
+      <c r="N69">
+        <v>-36.8663408</v>
+      </c>
+      <c r="O69">
+        <v>-5.529951120000002</v>
+      </c>
+      <c r="P69">
+        <v>-31.33638968</v>
+      </c>
+      <c r="Q69">
+        <v>-23.03638968000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4264230873007364</v>
+      </c>
+      <c r="T69">
+        <v>3.197761673154865</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06667536505191801</v>
+      </c>
+      <c r="W69">
+        <v>0.222877922825602</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4445024336794533</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2920478271023963</v>
+      </c>
+      <c r="C70">
+        <v>-18.24455549215787</v>
+      </c>
+      <c r="D70">
+        <v>172.3194445078421</v>
+      </c>
+      <c r="E70">
+        <v>264.264</v>
+      </c>
+      <c r="F70">
+        <v>282.064</v>
+      </c>
+      <c r="G70">
+        <v>91.5</v>
+      </c>
+      <c r="H70">
+        <v>397</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>37.8</v>
+      </c>
+      <c r="K70">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L70">
+        <v>29.5</v>
+      </c>
+      <c r="M70">
+        <v>67.35688320000001</v>
+      </c>
+      <c r="N70">
+        <v>-37.85688320000001</v>
+      </c>
+      <c r="O70">
+        <v>-5.678532480000003</v>
+      </c>
+      <c r="P70">
+        <v>-32.17835072000001</v>
+      </c>
+      <c r="Q70">
+        <v>-23.87835072000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4385363087788843</v>
+      </c>
+      <c r="T70">
+        <v>3.297691725440953</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06569484497762509</v>
+      </c>
+      <c r="W70">
+        <v>0.2231120710193431</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.4379656331841673</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2940478271023964</v>
+      </c>
+      <c r="C71">
+        <v>-23.74276831444939</v>
+      </c>
+      <c r="D71">
+        <v>170.9692316855507</v>
+      </c>
+      <c r="E71">
+        <v>268.412</v>
+      </c>
+      <c r="F71">
+        <v>286.212</v>
+      </c>
+      <c r="G71">
+        <v>91.5</v>
+      </c>
+      <c r="H71">
+        <v>397</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>37.8</v>
+      </c>
+      <c r="K71">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L71">
+        <v>29.5</v>
+      </c>
+      <c r="M71">
+        <v>68.34742560000001</v>
+      </c>
+      <c r="N71">
+        <v>-38.84742560000001</v>
+      </c>
+      <c r="O71">
+        <v>-5.827113840000002</v>
+      </c>
+      <c r="P71">
+        <v>-33.02031176000001</v>
+      </c>
+      <c r="Q71">
+        <v>-24.72031176000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.451431028416913</v>
+      </c>
+      <c r="T71">
+        <v>3.404068877874534</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06474274577505082</v>
+      </c>
+      <c r="W71">
+        <v>0.2233394323089179</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4316183051670054</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2960478271023963</v>
+      </c>
+      <c r="C72">
+        <v>-29.2199863965713</v>
+      </c>
+      <c r="D72">
+        <v>169.6400136034287</v>
+      </c>
+      <c r="E72">
+        <v>272.56</v>
+      </c>
+      <c r="F72">
+        <v>290.36</v>
+      </c>
+      <c r="G72">
+        <v>91.5</v>
+      </c>
+      <c r="H72">
+        <v>397</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>37.8</v>
+      </c>
+      <c r="K72">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L72">
+        <v>29.5</v>
+      </c>
+      <c r="M72">
+        <v>69.337968</v>
+      </c>
+      <c r="N72">
+        <v>-39.837968</v>
+      </c>
+      <c r="O72">
+        <v>-5.975695200000001</v>
+      </c>
+      <c r="P72">
+        <v>-33.8622728</v>
+      </c>
+      <c r="Q72">
+        <v>-25.5622728</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.46518539603081</v>
+      </c>
+      <c r="T72">
+        <v>3.517537840470351</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06381784940683581</v>
+      </c>
+      <c r="W72">
+        <v>0.2235602975616476</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4254523293789053</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2980478271023964</v>
+      </c>
+      <c r="C73">
+        <v>-34.67669563822238</v>
+      </c>
+      <c r="D73">
+        <v>168.3313043617776</v>
+      </c>
+      <c r="E73">
+        <v>276.708</v>
+      </c>
+      <c r="F73">
+        <v>294.508</v>
+      </c>
+      <c r="G73">
+        <v>91.5</v>
+      </c>
+      <c r="H73">
+        <v>397</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>37.8</v>
+      </c>
+      <c r="K73">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L73">
+        <v>29.5</v>
+      </c>
+      <c r="M73">
+        <v>70.3285104</v>
+      </c>
+      <c r="N73">
+        <v>-40.8285104</v>
+      </c>
+      <c r="O73">
+        <v>-6.124276560000001</v>
+      </c>
+      <c r="P73">
+        <v>-34.70423384</v>
+      </c>
+      <c r="Q73">
+        <v>-26.40423384</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4798883407215276</v>
+      </c>
+      <c r="T73">
+        <v>3.638832248762431</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06291900645744376</v>
+      </c>
+      <c r="W73">
+        <v>0.2237749412579624</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.419460043049625</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3000478271023963</v>
+      </c>
+      <c r="C74">
+        <v>-40.11336705975191</v>
+      </c>
+      <c r="D74">
+        <v>167.0426329402481</v>
+      </c>
+      <c r="E74">
+        <v>280.856</v>
+      </c>
+      <c r="F74">
+        <v>298.656</v>
+      </c>
+      <c r="G74">
+        <v>91.5</v>
+      </c>
+      <c r="H74">
+        <v>397</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>37.8</v>
+      </c>
+      <c r="K74">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L74">
+        <v>29.5</v>
+      </c>
+      <c r="M74">
+        <v>71.31905280000001</v>
+      </c>
+      <c r="N74">
+        <v>-41.81905280000001</v>
+      </c>
+      <c r="O74">
+        <v>-6.272857920000003</v>
+      </c>
+      <c r="P74">
+        <v>-35.54619488000001</v>
+      </c>
+      <c r="Q74">
+        <v>-27.24619488000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4956414957472964</v>
+      </c>
+      <c r="T74">
+        <v>3.76879054336109</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06204513136775704</v>
+      </c>
+      <c r="W74">
+        <v>0.2239836226293796</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4136342091183801</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3020478271023963</v>
+      </c>
+      <c r="C75">
+        <v>-45.53045736738261</v>
+      </c>
+      <c r="D75">
+        <v>165.7735426326174</v>
+      </c>
+      <c r="E75">
+        <v>285.004</v>
+      </c>
+      <c r="F75">
+        <v>302.804</v>
+      </c>
+      <c r="G75">
+        <v>91.5</v>
+      </c>
+      <c r="H75">
+        <v>397</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>37.8</v>
+      </c>
+      <c r="K75">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L75">
+        <v>29.5</v>
+      </c>
+      <c r="M75">
+        <v>72.3095952</v>
+      </c>
+      <c r="N75">
+        <v>-42.8095952</v>
+      </c>
+      <c r="O75">
+        <v>-6.421439280000001</v>
+      </c>
+      <c r="P75">
+        <v>-36.38815592</v>
+      </c>
+      <c r="Q75">
+        <v>-28.08815592000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5125615511453443</v>
+      </c>
+      <c r="T75">
+        <v>3.908375378300389</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06119519806134941</v>
+      </c>
+      <c r="W75">
+        <v>0.2241865867029498</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4079679870756626</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3040478271023964</v>
+      </c>
+      <c r="C76">
+        <v>-50.92840949286131</v>
+      </c>
+      <c r="D76">
+        <v>164.5235905071387</v>
+      </c>
+      <c r="E76">
+        <v>289.152</v>
+      </c>
+      <c r="F76">
+        <v>306.952</v>
+      </c>
+      <c r="G76">
+        <v>91.5</v>
+      </c>
+      <c r="H76">
+        <v>397</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>37.8</v>
+      </c>
+      <c r="K76">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L76">
+        <v>29.5</v>
+      </c>
+      <c r="M76">
+        <v>73.3001376</v>
+      </c>
+      <c r="N76">
+        <v>-43.8001376</v>
+      </c>
+      <c r="O76">
+        <v>-6.570020640000001</v>
+      </c>
+      <c r="P76">
+        <v>-37.23011696</v>
+      </c>
+      <c r="Q76">
+        <v>-28.93011696</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5307831492663193</v>
+      </c>
+      <c r="T76">
+        <v>4.05869750823502</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06036823592538523</v>
+      </c>
+      <c r="W76">
+        <v>0.224384065261018</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4024549061692348</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3060478271023964</v>
+      </c>
+      <c r="C77">
+        <v>-56.30765310887847</v>
+      </c>
+      <c r="D77">
+        <v>163.2923468911216</v>
+      </c>
+      <c r="E77">
+        <v>293.3</v>
+      </c>
+      <c r="F77">
+        <v>311.1</v>
+      </c>
+      <c r="G77">
+        <v>91.5</v>
+      </c>
+      <c r="H77">
+        <v>397</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>37.8</v>
+      </c>
+      <c r="K77">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L77">
+        <v>29.5</v>
+      </c>
+      <c r="M77">
+        <v>74.29068000000001</v>
+      </c>
+      <c r="N77">
+        <v>-44.79068000000001</v>
+      </c>
+      <c r="O77">
+        <v>-6.718602000000002</v>
+      </c>
+      <c r="P77">
+        <v>-38.072078</v>
+      </c>
+      <c r="Q77">
+        <v>-29.77207800000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.550462475236972</v>
+      </c>
+      <c r="T77">
+        <v>4.221045408564421</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05956332611304675</v>
+      </c>
+      <c r="W77">
+        <v>0.2245762777242045</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3970888407536449</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3080478271023963</v>
+      </c>
+      <c r="C78">
+        <v>-61.66860512151635</v>
+      </c>
+      <c r="D78">
+        <v>162.0793948784836</v>
+      </c>
+      <c r="E78">
+        <v>297.448</v>
+      </c>
+      <c r="F78">
+        <v>315.248</v>
+      </c>
+      <c r="G78">
+        <v>91.5</v>
+      </c>
+      <c r="H78">
+        <v>397</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>37.8</v>
+      </c>
+      <c r="K78">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L78">
+        <v>29.5</v>
+      </c>
+      <c r="M78">
+        <v>75.2812224</v>
+      </c>
+      <c r="N78">
+        <v>-45.7812224</v>
+      </c>
+      <c r="O78">
+        <v>-6.867183360000002</v>
+      </c>
+      <c r="P78">
+        <v>-38.91403904000001</v>
+      </c>
+      <c r="Q78">
+        <v>-30.61403904000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5717817450385125</v>
+      </c>
+      <c r="T78">
+        <v>4.396922300587938</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05877959813787509</v>
+      </c>
+      <c r="W78">
+        <v>0.2247634319646754</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3918639875858339</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3100478271023963</v>
+      </c>
+      <c r="C79">
+        <v>-67.01167014091135</v>
+      </c>
+      <c r="D79">
+        <v>160.8843298590887</v>
+      </c>
+      <c r="E79">
+        <v>301.596</v>
+      </c>
+      <c r="F79">
+        <v>319.396</v>
+      </c>
+      <c r="G79">
+        <v>91.5</v>
+      </c>
+      <c r="H79">
+        <v>397</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>37.8</v>
+      </c>
+      <c r="K79">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L79">
+        <v>29.5</v>
+      </c>
+      <c r="M79">
+        <v>76.27176480000001</v>
+      </c>
+      <c r="N79">
+        <v>-46.77176480000001</v>
+      </c>
+      <c r="O79">
+        <v>-7.015764720000004</v>
+      </c>
+      <c r="P79">
+        <v>-39.75600008000001</v>
+      </c>
+      <c r="Q79">
+        <v>-31.45600008000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5949548643880129</v>
+      </c>
+      <c r="T79">
+        <v>4.588092835396109</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05801622673348709</v>
+      </c>
+      <c r="W79">
+        <v>0.2249457250560433</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3867748448899139</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3120478271023963</v>
+      </c>
+      <c r="C80">
+        <v>-72.33724093124596</v>
+      </c>
+      <c r="D80">
+        <v>159.7067590687541</v>
+      </c>
+      <c r="E80">
+        <v>305.744</v>
+      </c>
+      <c r="F80">
+        <v>323.544</v>
+      </c>
+      <c r="G80">
+        <v>91.5</v>
+      </c>
+      <c r="H80">
+        <v>397</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>37.8</v>
+      </c>
+      <c r="K80">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L80">
+        <v>29.5</v>
+      </c>
+      <c r="M80">
+        <v>77.26230720000001</v>
+      </c>
+      <c r="N80">
+        <v>-47.76230720000001</v>
+      </c>
+      <c r="O80">
+        <v>-7.164346080000002</v>
+      </c>
+      <c r="P80">
+        <v>-40.59796112000001</v>
+      </c>
+      <c r="Q80">
+        <v>-32.29796112000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6202346309511046</v>
+      </c>
+      <c r="T80">
+        <v>4.796642509732297</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05727242895485265</v>
+      </c>
+      <c r="W80">
+        <v>0.2251233439655812</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3818161930323509</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3140478271023963</v>
+      </c>
+      <c r="C81">
+        <v>-77.64569884112319</v>
+      </c>
+      <c r="D81">
+        <v>158.5463011588768</v>
+      </c>
+      <c r="E81">
+        <v>309.892</v>
+      </c>
+      <c r="F81">
+        <v>327.692</v>
+      </c>
+      <c r="G81">
+        <v>91.5</v>
+      </c>
+      <c r="H81">
+        <v>397</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>37.8</v>
+      </c>
+      <c r="K81">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L81">
+        <v>29.5</v>
+      </c>
+      <c r="M81">
+        <v>78.2528496</v>
+      </c>
+      <c r="N81">
+        <v>-48.7528496</v>
+      </c>
+      <c r="O81">
+        <v>-7.312927440000002</v>
+      </c>
+      <c r="P81">
+        <v>-41.43992216</v>
+      </c>
+      <c r="Q81">
+        <v>-33.13992216</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6479219943297285</v>
+      </c>
+      <c r="T81">
+        <v>5.025054057814787</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05654746149972793</v>
+      </c>
+      <c r="W81">
+        <v>0.225296466193865</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3769830766648529</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3160478271023964</v>
+      </c>
+      <c r="C82">
+        <v>-82.93741421531317</v>
+      </c>
+      <c r="D82">
+        <v>157.4025857846869</v>
+      </c>
+      <c r="E82">
+        <v>314.04</v>
+      </c>
+      <c r="F82">
+        <v>331.84</v>
+      </c>
+      <c r="G82">
+        <v>91.5</v>
+      </c>
+      <c r="H82">
+        <v>397</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>37.8</v>
+      </c>
+      <c r="K82">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L82">
+        <v>29.5</v>
+      </c>
+      <c r="M82">
+        <v>79.24339200000001</v>
+      </c>
+      <c r="N82">
+        <v>-49.74339200000001</v>
+      </c>
+      <c r="O82">
+        <v>-7.461508800000003</v>
+      </c>
+      <c r="P82">
+        <v>-42.28188320000001</v>
+      </c>
+      <c r="Q82">
+        <v>-33.98188320000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6783780940462152</v>
+      </c>
+      <c r="T82">
+        <v>5.276306760705527</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05584061823098133</v>
+      </c>
+      <c r="W82">
+        <v>0.2254652603664417</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3722707882065421</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3180478271023963</v>
+      </c>
+      <c r="C83">
+        <v>-88.21274678880505</v>
+      </c>
+      <c r="D83">
+        <v>156.275253211195</v>
+      </c>
+      <c r="E83">
+        <v>318.188</v>
+      </c>
+      <c r="F83">
+        <v>335.9880000000001</v>
+      </c>
+      <c r="G83">
+        <v>91.5</v>
+      </c>
+      <c r="H83">
+        <v>397</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>37.8</v>
+      </c>
+      <c r="K83">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L83">
+        <v>29.5</v>
+      </c>
+      <c r="M83">
+        <v>80.23393440000002</v>
+      </c>
+      <c r="N83">
+        <v>-50.73393440000002</v>
+      </c>
+      <c r="O83">
+        <v>-7.610090160000005</v>
+      </c>
+      <c r="P83">
+        <v>-43.12384424000002</v>
+      </c>
+      <c r="Q83">
+        <v>-34.82384424000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.7120400989960158</v>
+      </c>
+      <c r="T83">
+        <v>5.554007116532134</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05515122788245069</v>
+      </c>
+      <c r="W83">
+        <v>0.2256298867816708</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3676748525496711</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3200478271023963</v>
+      </c>
+      <c r="C84">
+        <v>-93.47204606404742</v>
+      </c>
+      <c r="D84">
+        <v>155.1639539359526</v>
+      </c>
+      <c r="E84">
+        <v>322.336</v>
+      </c>
+      <c r="F84">
+        <v>340.136</v>
+      </c>
+      <c r="G84">
+        <v>91.5</v>
+      </c>
+      <c r="H84">
+        <v>397</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>37.8</v>
+      </c>
+      <c r="K84">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L84">
+        <v>29.5</v>
+      </c>
+      <c r="M84">
+        <v>81.22447680000001</v>
+      </c>
+      <c r="N84">
+        <v>-51.72447680000001</v>
+      </c>
+      <c r="O84">
+        <v>-7.758671520000002</v>
+      </c>
+      <c r="P84">
+        <v>-43.96580528</v>
+      </c>
+      <c r="Q84">
+        <v>-35.66580528000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7494423267180168</v>
+      </c>
+      <c r="T84">
+        <v>5.862563067450586</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05447865193266472</v>
+      </c>
+      <c r="W84">
+        <v>0.2257904979184797</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3631910128844313</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3220478271023963</v>
+      </c>
+      <c r="C85">
+        <v>-98.7156516722053</v>
+      </c>
+      <c r="D85">
+        <v>154.0683483277948</v>
+      </c>
+      <c r="E85">
+        <v>326.484</v>
+      </c>
+      <c r="F85">
+        <v>344.284</v>
+      </c>
+      <c r="G85">
+        <v>91.5</v>
+      </c>
+      <c r="H85">
+        <v>397</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>37.8</v>
+      </c>
+      <c r="K85">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L85">
+        <v>29.5</v>
+      </c>
+      <c r="M85">
+        <v>82.21501920000001</v>
+      </c>
+      <c r="N85">
+        <v>-52.71501920000001</v>
+      </c>
+      <c r="O85">
+        <v>-7.907252880000003</v>
+      </c>
+      <c r="P85">
+        <v>-44.80776632000001</v>
+      </c>
+      <c r="Q85">
+        <v>-36.50776632000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.791244816524959</v>
+      </c>
+      <c r="T85">
+        <v>6.207419718477091</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05382228263227116</v>
+      </c>
+      <c r="W85">
+        <v>0.2259472389074137</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3588152175484743</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3240478271023963</v>
+      </c>
+      <c r="C86">
+        <v>-103.94389371922</v>
+      </c>
+      <c r="D86">
+        <v>152.98810628078</v>
+      </c>
+      <c r="E86">
+        <v>330.632</v>
+      </c>
+      <c r="F86">
+        <v>348.432</v>
+      </c>
+      <c r="G86">
+        <v>91.5</v>
+      </c>
+      <c r="H86">
+        <v>397</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>37.8</v>
+      </c>
+      <c r="K86">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L86">
+        <v>29.5</v>
+      </c>
+      <c r="M86">
+        <v>83.20556160000001</v>
+      </c>
+      <c r="N86">
+        <v>-53.70556160000001</v>
+      </c>
+      <c r="O86">
+        <v>-8.055834240000003</v>
+      </c>
+      <c r="P86">
+        <v>-45.64972736000001</v>
+      </c>
+      <c r="Q86">
+        <v>-37.34972736000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8382726175577686</v>
+      </c>
+      <c r="T86">
+        <v>6.595383450881906</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05318154117236318</v>
+      </c>
+      <c r="W86">
+        <v>0.2261002479680397</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3545436078157544</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3260478271023963</v>
+      </c>
+      <c r="C87">
+        <v>-109.1570931174124</v>
+      </c>
+      <c r="D87">
+        <v>151.9229068825876</v>
+      </c>
+      <c r="E87">
+        <v>334.78</v>
+      </c>
+      <c r="F87">
+        <v>352.58</v>
+      </c>
+      <c r="G87">
+        <v>91.5</v>
+      </c>
+      <c r="H87">
+        <v>397</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>37.8</v>
+      </c>
+      <c r="K87">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L87">
+        <v>29.5</v>
+      </c>
+      <c r="M87">
+        <v>84.19610400000001</v>
+      </c>
+      <c r="N87">
+        <v>-54.69610400000001</v>
+      </c>
+      <c r="O87">
+        <v>-8.204415600000003</v>
+      </c>
+      <c r="P87">
+        <v>-46.4916884</v>
+      </c>
+      <c r="Q87">
+        <v>-38.1916884</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8915707920616198</v>
+      </c>
+      <c r="T87">
+        <v>7.0350756809407</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05255587598210008</v>
+      </c>
+      <c r="W87">
+        <v>0.2262496568154745</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3503725065473338</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3280478271023963</v>
+      </c>
+      <c r="C88">
+        <v>-114.3555619033287</v>
+      </c>
+      <c r="D88">
+        <v>150.8724380966713</v>
+      </c>
+      <c r="E88">
+        <v>338.928</v>
+      </c>
+      <c r="F88">
+        <v>356.728</v>
+      </c>
+      <c r="G88">
+        <v>91.5</v>
+      </c>
+      <c r="H88">
+        <v>397</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>37.8</v>
+      </c>
+      <c r="K88">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L88">
+        <v>29.5</v>
+      </c>
+      <c r="M88">
+        <v>85.1866464</v>
+      </c>
+      <c r="N88">
+        <v>-55.6866464</v>
+      </c>
+      <c r="O88">
+        <v>-8.35299696</v>
+      </c>
+      <c r="P88">
+        <v>-47.33364944</v>
+      </c>
+      <c r="Q88">
+        <v>-39.03364944</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9524829914945927</v>
+      </c>
+      <c r="T88">
+        <v>7.537581086722179</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05194476114509892</v>
+      </c>
+      <c r="W88">
+        <v>0.2263955910385504</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3462984076339928</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3300478271023963</v>
+      </c>
+      <c r="C89">
+        <v>-119.53960354249</v>
+      </c>
+      <c r="D89">
+        <v>149.83639645751</v>
+      </c>
+      <c r="E89">
+        <v>343.076</v>
+      </c>
+      <c r="F89">
+        <v>360.876</v>
+      </c>
+      <c r="G89">
+        <v>91.5</v>
+      </c>
+      <c r="H89">
+        <v>397</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>37.8</v>
+      </c>
+      <c r="K89">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L89">
+        <v>29.5</v>
+      </c>
+      <c r="M89">
+        <v>86.17718880000001</v>
+      </c>
+      <c r="N89">
+        <v>-56.67718880000001</v>
+      </c>
+      <c r="O89">
+        <v>-8.501578320000004</v>
+      </c>
+      <c r="P89">
+        <v>-48.17561048</v>
+      </c>
+      <c r="Q89">
+        <v>-39.87561048000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.022766298532638</v>
+      </c>
+      <c r="T89">
+        <v>8.11739501647004</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05134769492504031</v>
+      </c>
+      <c r="W89">
+        <v>0.2265381704519004</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3423179661669353</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3320478271023963</v>
+      </c>
+      <c r="C90">
+        <v>-124.709513221672</v>
+      </c>
+      <c r="D90">
+        <v>148.814486778328</v>
+      </c>
+      <c r="E90">
+        <v>347.224</v>
+      </c>
+      <c r="F90">
+        <v>365.024</v>
+      </c>
+      <c r="G90">
+        <v>91.5</v>
+      </c>
+      <c r="H90">
+        <v>397</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>37.8</v>
+      </c>
+      <c r="K90">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L90">
+        <v>29.5</v>
+      </c>
+      <c r="M90">
+        <v>87.16773120000001</v>
+      </c>
+      <c r="N90">
+        <v>-57.66773120000001</v>
+      </c>
+      <c r="O90">
+        <v>-8.650159680000002</v>
+      </c>
+      <c r="P90">
+        <v>-49.01757152</v>
+      </c>
+      <c r="Q90">
+        <v>-40.71757152000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.104763490077025</v>
+      </c>
+      <c r="T90">
+        <v>8.793844601175877</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05076419839180121</v>
+      </c>
+      <c r="W90">
+        <v>0.2266775094240379</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3384279892786747</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3340478271023963</v>
+      </c>
+      <c r="C91">
+        <v>-129.8655781293044</v>
+      </c>
+      <c r="D91">
+        <v>147.8064218706956</v>
+      </c>
+      <c r="E91">
+        <v>351.372</v>
+      </c>
+      <c r="F91">
+        <v>369.172</v>
+      </c>
+      <c r="G91">
+        <v>91.5</v>
+      </c>
+      <c r="H91">
+        <v>397</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>37.8</v>
+      </c>
+      <c r="K91">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L91">
+        <v>29.5</v>
+      </c>
+      <c r="M91">
+        <v>88.15827360000002</v>
+      </c>
+      <c r="N91">
+        <v>-58.65827360000002</v>
+      </c>
+      <c r="O91">
+        <v>-8.798741040000003</v>
+      </c>
+      <c r="P91">
+        <v>-49.85953256000001</v>
+      </c>
+      <c r="Q91">
+        <v>-41.55953256000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.201669261902209</v>
+      </c>
+      <c r="T91">
+        <v>9.593285019464593</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05019381414020794</v>
+      </c>
+      <c r="W91">
+        <v>0.2268137171833184</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3346254276013861</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3360478271023963</v>
+      </c>
+      <c r="C92">
+        <v>-135.0080777245514</v>
+      </c>
+      <c r="D92">
+        <v>146.8119222754486</v>
+      </c>
+      <c r="E92">
+        <v>355.52</v>
+      </c>
+      <c r="F92">
+        <v>373.32</v>
+      </c>
+      <c r="G92">
+        <v>91.5</v>
+      </c>
+      <c r="H92">
+        <v>397</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>37.8</v>
+      </c>
+      <c r="K92">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L92">
+        <v>29.5</v>
+      </c>
+      <c r="M92">
+        <v>89.148816</v>
+      </c>
+      <c r="N92">
+        <v>-59.648816</v>
+      </c>
+      <c r="O92">
+        <v>-8.947322400000001</v>
+      </c>
+      <c r="P92">
+        <v>-50.70149359999999</v>
+      </c>
+      <c r="Q92">
+        <v>-42.40149359999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.31795618809243</v>
+      </c>
+      <c r="T92">
+        <v>10.55261352141105</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04963610509420563</v>
+      </c>
+      <c r="W92">
+        <v>0.2269468981035037</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3309073672947042</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3380478271023963</v>
+      </c>
+      <c r="C93">
+        <v>-140.1372839956013</v>
+      </c>
+      <c r="D93">
+        <v>145.8307160043988</v>
+      </c>
+      <c r="E93">
+        <v>359.668</v>
+      </c>
+      <c r="F93">
+        <v>377.468</v>
+      </c>
+      <c r="G93">
+        <v>91.5</v>
+      </c>
+      <c r="H93">
+        <v>397</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>37.8</v>
+      </c>
+      <c r="K93">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L93">
+        <v>29.5</v>
+      </c>
+      <c r="M93">
+        <v>90.13935840000001</v>
+      </c>
+      <c r="N93">
+        <v>-60.63935840000001</v>
+      </c>
+      <c r="O93">
+        <v>-9.095903760000002</v>
+      </c>
+      <c r="P93">
+        <v>-51.54345464000001</v>
+      </c>
+      <c r="Q93">
+        <v>-43.24345464000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.460084653436034</v>
+      </c>
+      <c r="T93">
+        <v>11.72512613490117</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0490906533898737</v>
+      </c>
+      <c r="W93">
+        <v>0.2270771519704982</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.327271022599158</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3400478271023963</v>
+      </c>
+      <c r="C94">
+        <v>-145.2534617076671</v>
+      </c>
+      <c r="D94">
+        <v>144.8625382923329</v>
+      </c>
+      <c r="E94">
+        <v>363.816</v>
+      </c>
+      <c r="F94">
+        <v>381.616</v>
+      </c>
+      <c r="G94">
+        <v>91.5</v>
+      </c>
+      <c r="H94">
+        <v>397</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>37.8</v>
+      </c>
+      <c r="K94">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L94">
+        <v>29.5</v>
+      </c>
+      <c r="M94">
+        <v>91.12990080000002</v>
+      </c>
+      <c r="N94">
+        <v>-61.62990080000002</v>
+      </c>
+      <c r="O94">
+        <v>-9.244485120000004</v>
+      </c>
+      <c r="P94">
+        <v>-52.38541568000001</v>
+      </c>
+      <c r="Q94">
+        <v>-44.08541568000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.637745235115538</v>
+      </c>
+      <c r="T94">
+        <v>13.19076690176382</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04855705933128811</v>
+      </c>
+      <c r="W94">
+        <v>0.2272045742316884</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3237137288752541</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3420478271023963</v>
+      </c>
+      <c r="C95">
+        <v>-150.3568686411744</v>
+      </c>
+      <c r="D95">
+        <v>143.9071313588256</v>
+      </c>
+      <c r="E95">
+        <v>367.964</v>
+      </c>
+      <c r="F95">
+        <v>385.764</v>
+      </c>
+      <c r="G95">
+        <v>91.5</v>
+      </c>
+      <c r="H95">
+        <v>397</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>37.8</v>
+      </c>
+      <c r="K95">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L95">
+        <v>29.5</v>
+      </c>
+      <c r="M95">
+        <v>92.12044320000001</v>
+      </c>
+      <c r="N95">
+        <v>-62.62044320000001</v>
+      </c>
+      <c r="O95">
+        <v>-9.393066480000003</v>
+      </c>
+      <c r="P95">
+        <v>-53.22737672000001</v>
+      </c>
+      <c r="Q95">
+        <v>-44.92737672000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.866165982989187</v>
+      </c>
+      <c r="T95">
+        <v>15.07516217344437</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04803494041374738</v>
+      </c>
+      <c r="W95">
+        <v>0.2273292562291971</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3202329360916492</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3440478271023963</v>
+      </c>
+      <c r="C96">
+        <v>-155.4477558205846</v>
+      </c>
+      <c r="D96">
+        <v>142.9642441794155</v>
+      </c>
+      <c r="E96">
+        <v>372.112</v>
+      </c>
+      <c r="F96">
+        <v>389.912</v>
+      </c>
+      <c r="G96">
+        <v>91.5</v>
+      </c>
+      <c r="H96">
+        <v>397</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>37.8</v>
+      </c>
+      <c r="K96">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L96">
+        <v>29.5</v>
+      </c>
+      <c r="M96">
+        <v>93.11098560000001</v>
+      </c>
+      <c r="N96">
+        <v>-63.61098560000001</v>
+      </c>
+      <c r="O96">
+        <v>-9.541647840000003</v>
+      </c>
+      <c r="P96">
+        <v>-54.06933776</v>
+      </c>
+      <c r="Q96">
+        <v>-45.76933776000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.170726980154052</v>
+      </c>
+      <c r="T96">
+        <v>17.58768920235177</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04752393040934581</v>
+      </c>
+      <c r="W96">
+        <v>0.2274512854182482</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3168262027289721</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3460478271023963</v>
+      </c>
+      <c r="C97">
+        <v>-160.5263677342811</v>
+      </c>
+      <c r="D97">
+        <v>142.033632265719</v>
+      </c>
+      <c r="E97">
+        <v>376.26</v>
+      </c>
+      <c r="F97">
+        <v>394.0600000000001</v>
+      </c>
+      <c r="G97">
+        <v>91.5</v>
+      </c>
+      <c r="H97">
+        <v>397</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>37.8</v>
+      </c>
+      <c r="K97">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L97">
+        <v>29.5</v>
+      </c>
+      <c r="M97">
+        <v>94.10152800000002</v>
+      </c>
+      <c r="N97">
+        <v>-64.60152800000002</v>
+      </c>
+      <c r="O97">
+        <v>-9.690229200000005</v>
+      </c>
+      <c r="P97">
+        <v>-54.91129880000001</v>
+      </c>
+      <c r="Q97">
+        <v>-46.61129880000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.597112376184864</v>
+      </c>
+      <c r="T97">
+        <v>21.10522704282213</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04702367851030007</v>
+      </c>
+      <c r="W97">
+        <v>0.2275707455717403</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3134911900686671</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3480478271023963</v>
+      </c>
+      <c r="C98">
+        <v>-165.5929425459234</v>
+      </c>
+      <c r="D98">
+        <v>141.1150574540765</v>
+      </c>
+      <c r="E98">
+        <v>380.408</v>
+      </c>
+      <c r="F98">
+        <v>398.208</v>
+      </c>
+      <c r="G98">
+        <v>91.5</v>
+      </c>
+      <c r="H98">
+        <v>397</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>37.8</v>
+      </c>
+      <c r="K98">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L98">
+        <v>29.5</v>
+      </c>
+      <c r="M98">
+        <v>95.0920704</v>
+      </c>
+      <c r="N98">
+        <v>-65.5920704</v>
+      </c>
+      <c r="O98">
+        <v>-9.838810560000001</v>
+      </c>
+      <c r="P98">
+        <v>-55.75325984</v>
+      </c>
+      <c r="Q98">
+        <v>-47.45325984</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.236690470231073</v>
+      </c>
+      <c r="T98">
+        <v>26.38153380352761</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04653384852581778</v>
+      </c>
+      <c r="W98">
+        <v>0.2276877169720347</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3102256568387852</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3500478271023963</v>
+      </c>
+      <c r="C99">
+        <v>-170.6477122976535</v>
+      </c>
+      <c r="D99">
+        <v>140.2082877023465</v>
+      </c>
+      <c r="E99">
+        <v>384.556</v>
+      </c>
+      <c r="F99">
+        <v>402.356</v>
+      </c>
+      <c r="G99">
+        <v>91.5</v>
+      </c>
+      <c r="H99">
+        <v>397</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>37.8</v>
+      </c>
+      <c r="K99">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L99">
+        <v>29.5</v>
+      </c>
+      <c r="M99">
+        <v>96.08261280000001</v>
+      </c>
+      <c r="N99">
+        <v>-66.58261280000001</v>
+      </c>
+      <c r="O99">
+        <v>-9.987391920000002</v>
+      </c>
+      <c r="P99">
+        <v>-56.59522088000001</v>
+      </c>
+      <c r="Q99">
+        <v>-48.29522088000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.302653960308097</v>
+      </c>
+      <c r="T99">
+        <v>35.17537840470348</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0460541181286444</v>
+      </c>
+      <c r="W99">
+        <v>0.2278022765908797</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3070274541909626</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3520478271023963</v>
+      </c>
+      <c r="C100">
+        <v>-175.6909031055152</v>
+      </c>
+      <c r="D100">
+        <v>139.3130968944849</v>
+      </c>
+      <c r="E100">
+        <v>388.704</v>
+      </c>
+      <c r="F100">
+        <v>406.504</v>
+      </c>
+      <c r="G100">
+        <v>91.5</v>
+      </c>
+      <c r="H100">
+        <v>397</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>37.8</v>
+      </c>
+      <c r="K100">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L100">
+        <v>29.5</v>
+      </c>
+      <c r="M100">
+        <v>97.07315520000002</v>
+      </c>
+      <c r="N100">
+        <v>-67.57315520000002</v>
+      </c>
+      <c r="O100">
+        <v>-10.13597328</v>
+      </c>
+      <c r="P100">
+        <v>-57.43718192000001</v>
+      </c>
+      <c r="Q100">
+        <v>-49.13718192000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.434580940462145</v>
+      </c>
+      <c r="T100">
+        <v>52.76306760705521</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04558417814773986</v>
+      </c>
+      <c r="W100">
+        <v>0.2279144982583197</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3038945209849323</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3540478271023964</v>
+      </c>
+      <c r="C101">
+        <v>-180.7227353474372</v>
+      </c>
+      <c r="D101">
+        <v>138.4292646525628</v>
+      </c>
+      <c r="E101">
+        <v>392.852</v>
+      </c>
+      <c r="F101">
+        <v>410.652</v>
+      </c>
+      <c r="G101">
+        <v>91.5</v>
+      </c>
+      <c r="H101">
+        <v>397</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>37.8</v>
+      </c>
+      <c r="K101">
+        <v>8.299999999999997</v>
+      </c>
+      <c r="L101">
+        <v>29.5</v>
+      </c>
+      <c r="M101">
+        <v>98.0636976</v>
+      </c>
+      <c r="N101">
+        <v>-68.5636976</v>
+      </c>
+      <c r="O101">
+        <v>-10.28455464</v>
+      </c>
+      <c r="P101">
+        <v>-58.27914295999999</v>
+      </c>
+      <c r="Q101">
+        <v>-49.97914296</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.83036188092429</v>
+      </c>
+      <c r="T101">
+        <v>105.5261352141104</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0451237319038233</v>
+      </c>
+      <c r="W101">
+        <v>0.228024452821367</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.300824879358822</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
